--- a/deliverables/Target_Cash_Flow_Investment_Capacity_Model.xlsx
+++ b/deliverables/Target_Cash_Flow_Investment_Capacity_Model.xlsx
@@ -24,7 +24,7 @@
     <sheet name="Limitations" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Executive Summary'!$A$1:$D$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Executive Summary'!$A$1:$D$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,7 +38,7 @@
     <numFmt numFmtId="166" formatCode="$0.00"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,8 +97,9 @@
       <color rgb="007F6000"/>
     </font>
     <font>
-      <b val="1"/>
-      <sz val="12"/>
+      <i val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -107,8 +108,25 @@
     </font>
     <font>
       <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
       <color rgb="00C00000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
     </font>
   </fonts>
   <fills count="4">
@@ -155,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -172,12 +190,17 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -198,10 +221,12 @@
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="9" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -291,7 +316,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>FY2030 Deployable Capacity by Scenario</a:t>
+              <a:t>FY2030 Remaining Deployable Headroom by Scenario</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -306,7 +331,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Executive Summary'!B16</f>
+              <f>'Executive Summary'!B23</f>
             </strRef>
           </tx>
           <spPr>
@@ -316,12 +341,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Executive Summary'!$A$17:$A$19</f>
+              <f>'Executive Summary'!$A$24:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Executive Summary'!$B$17:$B$19</f>
+              <f>'Executive Summary'!$B$24:$B$26</f>
             </numRef>
           </val>
         </ser>
@@ -958,13 +983,13 @@
           <t>Selected scenario:</t>
         </is>
       </c>
-      <c r="B2" s="24">
+      <c r="B2" s="27">
         <f>'Forecast Assumptions'!$C$2</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>Order of operations: 1) Operating cash generation 2) CapEx 3) Dividends 4) Minimum cash preservation 5) Scheduled debt 6) Incremental financing (always $0) 7) Discretionary repurchases 8) Ending cash.</t>
         </is>
@@ -1367,13 +1392,13 @@
           <t>Selected scenario:</t>
         </is>
       </c>
-      <c r="B2" s="24">
+      <c r="B2" s="27">
         <f>'Forecast Assumptions'!$C$2</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>Illustrative WACC inputs below (yellow) -- no live market-data source is available to this project (SEC filings only); see Sheet 15 (Limitations).</t>
         </is>
@@ -1392,7 +1417,7 @@
           <t>Risk-Free Rate</t>
         </is>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="25" t="n">
         <v>0.045</v>
       </c>
     </row>
@@ -1402,7 +1427,7 @@
           <t>Equity Risk Premium</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="25" t="n">
         <v>0.055</v>
       </c>
     </row>
@@ -1412,7 +1437,7 @@
           <t>Beta</t>
         </is>
       </c>
-      <c r="B8" s="26" t="n">
+      <c r="B8" s="32" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1422,7 +1447,7 @@
           <t>Target Equity Weight</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n">
+      <c r="B9" s="25" t="n">
         <v>0.85</v>
       </c>
     </row>
@@ -1432,7 +1457,7 @@
           <t>Target Debt Weight</t>
         </is>
       </c>
-      <c r="B10" s="22" t="n">
+      <c r="B10" s="25" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -1442,7 +1467,7 @@
           <t>Pre-Tax Cost of Debt</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n">
+      <c r="B11" s="25" t="n">
         <v>0.031</v>
       </c>
     </row>
@@ -1452,7 +1477,7 @@
           <t>Tax Rate (for WACC)</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n">
+      <c r="B12" s="25" t="n">
         <v>0.222</v>
       </c>
     </row>
@@ -1462,7 +1487,7 @@
           <t>Terminal Growth Rate</t>
         </is>
       </c>
-      <c r="B13" s="22" t="n">
+      <c r="B13" s="25" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -1472,7 +1497,7 @@
           <t>Cost of Equity (CAPM)</t>
         </is>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="21">
         <f>B6+B8*B7</f>
         <v/>
       </c>
@@ -1483,7 +1508,7 @@
           <t>After-Tax Cost of Debt</t>
         </is>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="21">
         <f>B11*(1-B12)</f>
         <v/>
       </c>
@@ -1494,7 +1519,7 @@
           <t>WACC</t>
         </is>
       </c>
-      <c r="B17" s="18">
+      <c r="B17" s="21">
         <f>B15*B9+B16*B10</f>
         <v/>
       </c>
@@ -1701,23 +1726,23 @@
           <t>Discount Factor</t>
         </is>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="33">
         <f>1/(1+$B$17)^1</f>
         <v/>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="33">
         <f>1/(1+$B$17)^2</f>
         <v/>
       </c>
-      <c r="F26" s="27">
+      <c r="F26" s="33">
         <f>1/(1+$B$17)^3</f>
         <v/>
       </c>
-      <c r="G26" s="27">
+      <c r="G26" s="33">
         <f>1/(1+$B$17)^4</f>
         <v/>
       </c>
-      <c r="H26" s="27">
+      <c r="H26" s="33">
         <f>1/(1+$B$17)^5</f>
         <v/>
       </c>
@@ -1806,7 +1831,7 @@
           <t>Enterprise Value</t>
         </is>
       </c>
-      <c r="B34" s="28">
+      <c r="B34" s="13">
         <f>B30+B33</f>
         <v/>
       </c>
@@ -1817,7 +1842,7 @@
           <t>Net Debt (FY2025 actual: total_debt_gaap - cash)</t>
         </is>
       </c>
-      <c r="B35" s="23" t="n">
+      <c r="B35" s="26" t="n">
         <v>8855</v>
       </c>
     </row>
@@ -1827,7 +1852,7 @@
           <t>Equity Value</t>
         </is>
       </c>
-      <c r="B36" s="28">
+      <c r="B36" s="13">
         <f>B34-B35</f>
         <v/>
       </c>
@@ -1838,17 +1863,17 @@
           <t>Diluted Shares (FY2025 actual, millions)</t>
         </is>
       </c>
-      <c r="B37" s="23" t="n">
+      <c r="B37" s="26" t="n">
         <v>455.6</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="29" t="inlineStr">
+      <c r="A38" s="34" t="inlineStr">
         <is>
           <t>IMPLIED VALUE PER SHARE</t>
         </is>
       </c>
-      <c r="B38" s="30">
+      <c r="B38" s="35">
         <f>B36/B37</f>
         <v/>
       </c>
@@ -1883,7 +1908,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="19" t="inlineStr">
+      <c r="A43" s="22" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
@@ -1899,7 +1924,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="19" t="inlineStr">
+      <c r="A44" s="22" t="inlineStr">
         <is>
           <t>Upside</t>
         </is>
@@ -1915,7 +1940,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="19" t="inlineStr">
+      <c r="A45" s="22" t="inlineStr">
         <is>
           <t>Downside</t>
         </is>
@@ -1995,17 +2020,17 @@
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>Deployable Capacity</t>
+          <t>Legacy Gross Capacity (DEPRECATED)</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
-          <t>Cumulative Deployable Capacity</t>
+          <t>Legacy Cumulative (DEPRECATED)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="n">
+      <c r="A5" s="22" t="n">
         <v>-1</v>
       </c>
       <c r="B5" s="10" t="n">
@@ -2025,7 +2050,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="n">
+      <c r="A6" s="22" t="n">
         <v>-0.5</v>
       </c>
       <c r="B6" s="10" t="n">
@@ -2045,7 +2070,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="22" t="n">
         <v>0</v>
       </c>
       <c r="B7" s="10" t="n">
@@ -2065,7 +2090,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="n">
+      <c r="A8" s="22" t="n">
         <v>0.5</v>
       </c>
       <c r="B8" s="10" t="n">
@@ -2085,7 +2110,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="22" t="n">
         <v>1</v>
       </c>
       <c r="B9" s="10" t="n">
@@ -2134,17 +2159,17 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>Deployable Capacity</t>
+          <t>Legacy Gross Capacity (DEPRECATED)</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Cumulative Deployable Capacity</t>
+          <t>Legacy Cumulative (DEPRECATED)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="22" t="n">
         <v>-0.5</v>
       </c>
       <c r="B13" s="10" t="n">
@@ -2164,7 +2189,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="n">
+      <c r="A14" s="22" t="n">
         <v>-0.25</v>
       </c>
       <c r="B14" s="10" t="n">
@@ -2184,7 +2209,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="n">
+      <c r="A15" s="22" t="n">
         <v>0</v>
       </c>
       <c r="B15" s="10" t="n">
@@ -2204,7 +2229,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="n">
+      <c r="A16" s="22" t="n">
         <v>0.25</v>
       </c>
       <c r="B16" s="10" t="n">
@@ -2224,7 +2249,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="n">
+      <c r="A17" s="22" t="n">
         <v>0.5</v>
       </c>
       <c r="B17" s="10" t="n">
@@ -2273,17 +2298,17 @@
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Deployable Capacity</t>
+          <t>Legacy Gross Capacity (DEPRECATED)</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>Cumulative Deployable Capacity</t>
+          <t>Legacy Cumulative (DEPRECATED)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="n">
+      <c r="A21" s="22" t="n">
         <v>-0.5</v>
       </c>
       <c r="B21" s="10" t="n">
@@ -2303,7 +2328,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="n">
+      <c r="A22" s="22" t="n">
         <v>-0.25</v>
       </c>
       <c r="B22" s="10" t="n">
@@ -2323,7 +2348,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="19" t="n">
+      <c r="A23" s="22" t="n">
         <v>0</v>
       </c>
       <c r="B23" s="10" t="n">
@@ -2343,7 +2368,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="19" t="n">
+      <c r="A24" s="22" t="n">
         <v>0.25</v>
       </c>
       <c r="B24" s="10" t="n">
@@ -2363,7 +2388,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="n">
+      <c r="A25" s="22" t="n">
         <v>0.5</v>
       </c>
       <c r="B25" s="10" t="n">
@@ -2412,17 +2437,17 @@
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>Deployable Capacity</t>
+          <t>Legacy Gross Capacity (DEPRECATED)</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>Cumulative Deployable Capacity</t>
+          <t>Legacy Cumulative (DEPRECATED)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="19" t="n">
+      <c r="A29" s="22" t="n">
         <v>-0.5</v>
       </c>
       <c r="B29" s="10" t="n">
@@ -2442,7 +2467,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="n">
+      <c r="A30" s="22" t="n">
         <v>-0.25</v>
       </c>
       <c r="B30" s="10" t="n">
@@ -2462,7 +2487,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="19" t="n">
+      <c r="A31" s="22" t="n">
         <v>0</v>
       </c>
       <c r="B31" s="10" t="n">
@@ -2482,7 +2507,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="19" t="n">
+      <c r="A32" s="22" t="n">
         <v>0.25</v>
       </c>
       <c r="B32" s="10" t="n">
@@ -2502,7 +2527,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="19" t="n">
+      <c r="A33" s="22" t="n">
         <v>0.5</v>
       </c>
       <c r="B33" s="10" t="n">
@@ -2551,17 +2576,17 @@
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>Deployable Capacity</t>
+          <t>Legacy Gross Capacity (DEPRECATED)</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>Cumulative Deployable Capacity</t>
+          <t>Legacy Cumulative (DEPRECATED)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="19" t="n">
+      <c r="A37" s="22" t="n">
         <v>-1</v>
       </c>
       <c r="B37" s="10" t="n">
@@ -2581,7 +2606,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="19" t="n">
+      <c r="A38" s="22" t="n">
         <v>-0.5</v>
       </c>
       <c r="B38" s="10" t="n">
@@ -2601,7 +2626,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="19" t="n">
+      <c r="A39" s="22" t="n">
         <v>0</v>
       </c>
       <c r="B39" s="10" t="n">
@@ -2621,7 +2646,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="19" t="n">
+      <c r="A40" s="22" t="n">
         <v>0.5</v>
       </c>
       <c r="B40" s="10" t="n">
@@ -2641,7 +2666,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="19" t="n">
+      <c r="A41" s="22" t="n">
         <v>1</v>
       </c>
       <c r="B41" s="10" t="n">
@@ -2690,17 +2715,17 @@
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>Deployable Capacity</t>
+          <t>Legacy Gross Capacity (DEPRECATED)</t>
         </is>
       </c>
       <c r="F44" s="9" t="inlineStr">
         <is>
-          <t>Cumulative Deployable Capacity</t>
+          <t>Legacy Cumulative (DEPRECATED)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="19" t="n">
+      <c r="A45" s="22" t="n">
         <v>-1</v>
       </c>
       <c r="B45" s="10" t="n">
@@ -2720,7 +2745,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="19" t="n">
+      <c r="A46" s="22" t="n">
         <v>-0.5</v>
       </c>
       <c r="B46" s="10" t="n">
@@ -2740,7 +2765,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="19" t="n">
+      <c r="A47" s="22" t="n">
         <v>0</v>
       </c>
       <c r="B47" s="10" t="n">
@@ -2760,7 +2785,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="19" t="n">
+      <c r="A48" s="22" t="n">
         <v>0.5</v>
       </c>
       <c r="B48" s="10" t="n">
@@ -2780,7 +2805,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="19" t="n">
+      <c r="A49" s="22" t="n">
         <v>1</v>
       </c>
       <c r="B49" s="10" t="n">
@@ -2802,7 +2827,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Two-Variable: Revenue Growth x Gross Margin (FY2030 Deployable Capacity)</t>
+          <t>Two-Variable: Revenue Growth x Gross Margin (FY2030 Legacy Gross Capacity, DEPRECATED)</t>
         </is>
       </c>
     </row>
@@ -3183,183 +3208,183 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>0000027419-22-000007</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>2022-01-29</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>2022-03-09</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>0000027419-23-000015</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>2023-01-28</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>2023-03-08</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>0000027419-24-000032</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>2024-02-03</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>2024-03-13</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>0000027419-25-000018</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>2025-02-01</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>2025-03-12</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>0000027419-25-000101</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>10-Q</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>2025-05-30</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>0000027419-25-000118</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>10-Q</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>2025-08-29</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>0000027419-25-000126</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>10-Q</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>0000027419-26-000016</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>Lineage: every forecast fact traces to a historical annual_facts anchor, a prior forecast fact, or a forecast_assumptions row (1,533 forecast_lineage rows persisted; see docs/milestone_3_forecast_schema_proposal.md and the forecast_lineage table).</t>
         </is>
@@ -3381,7 +3406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3433,401 +3458,401 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>assumption_completeness</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n">
+      <c r="B5" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="19" t="n">
+      <c r="D5" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>capital_allocation_waterfall_reconciliation</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
+      <c r="B6" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="D6" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="19" t="n">
+      <c r="D6" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>cash_roll_forward</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n">
+      <c r="B7" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="D7" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="19" t="n">
+      <c r="D7" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>cfo_construction</t>
         </is>
       </c>
-      <c r="B8" s="19" t="n">
+      <c r="B8" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="D8" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="19" t="n">
+      <c r="D8" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>cumulative_capacity_no_double_counting</t>
         </is>
       </c>
-      <c r="B9" s="19" t="n">
+      <c r="B9" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="19" t="n">
+      <c r="D9" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>debt_roll_forward</t>
         </is>
       </c>
-      <c r="B10" s="19" t="n">
+      <c r="B10" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="D10" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="19" t="n">
+      <c r="D10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>eps_consistency</t>
         </is>
       </c>
-      <c r="B11" s="19" t="n">
+      <c r="B11" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="D11" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="19" t="n">
+      <c r="D11" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>fcf_calc</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n">
+      <c r="B12" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="D12" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="19" t="n">
+      <c r="D12" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>gross_profit_calc</t>
         </is>
       </c>
-      <c r="B13" s="19" t="n">
+      <c r="B13" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="C13" s="19" t="n">
+      <c r="C13" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="D13" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="19" t="n">
+      <c r="D13" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>information_cutoff_compliance</t>
         </is>
       </c>
-      <c r="B14" s="19" t="n">
+      <c r="B14" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="C14" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="19" t="n">
+      <c r="D14" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>lineage_completeness</t>
         </is>
       </c>
-      <c r="B15" s="19" t="n">
+      <c r="B15" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="19" t="n">
+      <c r="C15" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="D15" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="19" t="n">
+      <c r="D15" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>minimum_cash_compliance</t>
         </is>
       </c>
-      <c r="B16" s="19" t="n">
+      <c r="B16" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="C16" s="19" t="n">
+      <c r="C16" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="D16" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="19" t="n">
+      <c r="D16" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>no_finance_lease_double_counting</t>
         </is>
       </c>
-      <c r="B17" s="19" t="n">
+      <c r="B17" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="C17" s="19" t="n">
+      <c r="C17" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="D17" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="19" t="n">
+      <c r="D17" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>no_historical_forecast_mixing</t>
         </is>
       </c>
-      <c r="B18" s="19" t="n">
+      <c r="B18" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C18" s="19" t="n">
+      <c r="C18" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="19" t="n">
+      <c r="D18" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>operating_income_bridge</t>
         </is>
       </c>
-      <c r="B19" s="19" t="n">
+      <c r="B19" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="C19" s="19" t="n">
+      <c r="C19" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="D19" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="19" t="n">
+      <c r="D19" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>other_operating_cf_not_a_plug</t>
         </is>
       </c>
-      <c r="B20" s="19" t="n">
+      <c r="B20" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="C20" s="19" t="n">
+      <c r="C20" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="19" t="n">
+      <c r="D20" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>pretax_income_bridge</t>
         </is>
       </c>
-      <c r="B21" s="19" t="n">
+      <c r="B21" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="C21" s="19" t="n">
+      <c r="C21" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="D21" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="19" t="n">
+      <c r="D21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>revenue_recursion</t>
         </is>
       </c>
-      <c r="B22" s="19" t="n">
+      <c r="B22" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="C22" s="19" t="n">
+      <c r="C22" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="D22" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="19" t="n">
+      <c r="D22" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>scenario_ordering</t>
         </is>
       </c>
-      <c r="B23" s="19" t="n">
+      <c r="B23" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="C23" s="19" t="n">
+      <c r="C23" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="D23" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="19" t="n">
+      <c r="D23" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>tax_net_income_bridge</t>
         </is>
       </c>
-      <c r="B24" s="19" t="n">
+      <c r="B24" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="C24" s="19" t="n">
+      <c r="C24" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="D24" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="19" t="n">
+      <c r="D24" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>working_capital_sign_checks</t>
         </is>
       </c>
-      <c r="B25" s="19" t="n">
+      <c r="B25" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="C25" s="19" t="n">
+      <c r="C25" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="D25" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="19" t="n">
+      <c r="D25" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3868,98 +3893,98 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>ufcf_reconciles_to_levered_fcf</t>
         </is>
       </c>
-      <c r="B31" s="19" t="n">
+      <c r="B31" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="C31" s="19" t="n">
+      <c r="C31" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="D31" s="19" t="n">
+      <c r="D31" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>terminal_value_period_consistency</t>
         </is>
       </c>
-      <c r="B32" s="19" t="n">
+      <c r="B32" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="19" t="n">
+      <c r="C32" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="D32" s="19" t="n">
+      <c r="D32" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>no_debt_or_lease_double_counting</t>
         </is>
       </c>
-      <c r="B33" s="19" t="n">
+      <c r="B33" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="C33" s="19" t="n">
+      <c r="C33" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="D33" s="19" t="n">
+      <c r="D33" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>valuation_date_consistency</t>
         </is>
       </c>
-      <c r="B34" s="19" t="n">
+      <c r="B34" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="C34" s="19" t="n">
+      <c r="C34" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="D34" s="19" t="n">
+      <c r="D34" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>wacc_exceeds_terminal_growth</t>
         </is>
       </c>
-      <c r="B35" s="19" t="n">
+      <c r="B35" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="C35" s="19" t="n">
+      <c r="C35" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="D35" s="19" t="n">
+      <c r="D35" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>wacc_and_terminal_growth_scenario_invariant</t>
         </is>
       </c>
-      <c r="B36" s="19" t="n">
+      <c r="B36" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C36" s="19" t="n">
+      <c r="C36" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="19" t="n">
+      <c r="D36" s="22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3967,6 +3992,294 @@
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>TOTAL: 28 results, 0 failures</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Corrected Capacity Taxonomy (Milestone 9 correction): 13 named checks</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>WARNING</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>annual_source_use_reconciliation</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C42" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="D42" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t>capacity_accounted_for_reconciliation</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C43" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>capacity_mutually_exclusive</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C44" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="D44" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>cumulative_deployment_includes_repurchases</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>cumulative_excludes_repeated_balances</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C46" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>ending_cash_above_buffer_or_flagged</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C47" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="D47" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>headroom_never_negative</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C48" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="D48" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>mandatory_debt_not_double_deducted</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C49" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="D49" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="20" t="inlineStr">
+        <is>
+          <t>opening_excess_liquidity_excluded_from_generation</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C50" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="20" t="inlineStr">
+        <is>
+          <t>operating_fcf_reconciles</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C51" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="D51" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="20" t="inlineStr">
+        <is>
+          <t>post_dividend_generation_reconciles</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C52" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="D52" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="20" t="inlineStr">
+        <is>
+          <t>repurchases_in_discretionary_deployment</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C53" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="D53" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="20" t="inlineStr">
+        <is>
+          <t>scenario_and_cutoff_lineage_complete</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C54" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="D54" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL: 147 results, 0 failures (7 further structural/definitional proofs live in tests/unit/test_capacity_taxonomy.py)</t>
         </is>
       </c>
     </row>
@@ -3985,7 +4298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -3999,86 +4312,100 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>- investing_cash_flow is modeled as exactly -CapEx; no driver exists for other historical investing items.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>- No FX translation effect is modeled (implicitly zero).</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>- The near-term debt repayment reserve is proxied by each year's own fixed repayment assumption -- no disclosed maturity ladder exists.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>- 'Other operating cash adjustments' is a single flat scenario assumption, not decomposed into stock-comp/deferred-tax/other sub-components.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>- The seasonality stress overlay is grounded in exactly ONE year of real quarterly evidence (FY2025).</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>- The minimum-cash-buffer comparison evaluates 5 policies but endorses none as final.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>- DCF WACC components (risk-free rate, equity risk premium, beta) are illustrative, general-market inputs -- no live market-data source is in the registered source set.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>- DCF capital-structure weights are a target/policy split, not a market-value weight (which would require the market value of equity -- circular with the equity value being estimated).</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>- This workbook is a scenario-based model, NOT investment advice, a price target, or a prediction of Target's actual future results or stock price.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>- CapEx is modeled as a % of revenue with no maintenance-vs-growth split, since Target discloses no such split.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>- Dividends are modeled via a $/share growth proxy, not a disclosed per-share dividend policy statement.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>- No information after the FY2025 10-K cutoff (2026-03-11) is used anywhere in this workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>- Milestone 9 correction: the original 'DEPLOYABLE CAPACITY' headline (Sheet 9) was found to be arithmetically correct but economically ambiguous -- a gross, pre-discretionary ceiling that never subtracted that year's own repurchases. It is preserved, relabeled and deprecated, on Sheet 9 for backward compatibility; the corrected taxonomy (Self-Funded / Debt-Funded / Discretionary Deployment / Remaining Deployable Headroom) on Sheets 2 and 9 is now the executive-facing figure. See docs/investment_capacity_semantic_audit.md and docs/investment_capacity_correction_evidence.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>- strategic_investment, voluntary_debt_reduction, and other_discretionary_uses in the corrected taxonomy are structural $0 placeholders -- no policy lever for them has been modeled this round, following the same convention already established for management_selected_deployment.</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4222,98 +4549,161 @@
         <v>2082.64</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Deployable Capacity ($M)</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="n">
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Corrected Capacity Taxonomy (FY2030) -- see Sheet 9 for full detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Self-Funded Capacity Generated ($M)</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n">
         <v>6315.02</v>
       </c>
-      <c r="C10" s="10" t="n">
-        <v>3241.94</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>6087.52</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Implied DCF Value/Share ($)</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="n">
-        <v>107.29</v>
-      </c>
-      <c r="C11" s="12" t="n">
-        <v>138.32</v>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>61.55</v>
+      <c r="C12" s="13" t="n">
+        <v>3941.94</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>5887.52</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>Debt-Funded Capacity ($M)</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>700</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Discretionary Deployment ($M)</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>636.3099999999999</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>1498.44</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Remaining Deployable Headroom ($M)</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>6378.71</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>2743.5</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>6387.52</v>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Note: a higher-revenue scenario can show LOWER remaining headroom -- it may be deploying far more into buybacks/deleveraging (Upside), not generating less. See the FY2030 scenario bridges in docs/investment_capacity_correction_evidence.md and Sheet 9.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Implied DCF Value/Share ($)</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="n">
+        <v>107.29</v>
+      </c>
+      <c r="C18" s="15" t="n">
+        <v>138.32</v>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>61.55</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>Key question answered:</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>How much capital can Target safely deploy after funding operations, CapEx, dividends, minimum liquidity, and debt obligations? -- see Sheet 9 (Investment Capacity) for the full FY2026-FY2030 build for the selected scenario.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Deployable Capacity FY2030 ($M)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Remaining Deployable Headroom, FY2030 ($M)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>6315</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="B24" t="n">
+        <v>6378.7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Upside</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>3241.9</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="B25" t="n">
+        <v>2743.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Downside</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>6087.5</v>
+      <c r="B26" t="n">
+        <v>6387.5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
+    <mergeCell ref="A21:D21"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4626,19 +5016,19 @@
           <t>Diluted EPS ($)</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n">
+      <c r="B15" s="17" t="n">
         <v>14.1</v>
       </c>
-      <c r="C15" s="14" t="n">
+      <c r="C15" s="17" t="n">
         <v>5.98</v>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="17" t="n">
         <v>8.94</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="17" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F15" s="17" t="n">
         <v>8.130000000000001</v>
       </c>
     </row>
@@ -4863,7 +5253,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>Note: FY2023 was a 53-week fiscal year. All figures are the LATEST-RESTATED analytical view -- see Sheet 4 for the as-originally-filed vs. restated comparison.</t>
         </is>
@@ -4905,7 +5295,7 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>Target reclassified certain distribution-center costs between Cost of Sales and SG&amp;A in later filings (disclosed reclassification, FY2022-FY2023 restated views differ from the originally-filed views). Revenue is identical in both views every year -- only the COGS/SG&amp;A split moved.</t>
         </is>
@@ -4949,12 +5339,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="20" t="n">
         <v>2021</v>
       </c>
       <c r="C5" s="10" t="n">
@@ -4966,22 +5356,22 @@
       <c r="E5" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="F5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="20" t="n">
         <v>2022</v>
       </c>
       <c r="C6" s="10" t="n">
@@ -4993,22 +5383,22 @@
       <c r="E6" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="F6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="20" t="n">
         <v>2023</v>
       </c>
       <c r="C7" s="10" t="n">
@@ -5020,22 +5410,22 @@
       <c r="E7" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="F7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="20" t="n">
         <v>2024</v>
       </c>
       <c r="C8" s="10" t="n">
@@ -5047,22 +5437,22 @@
       <c r="E8" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="F8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="20" t="n">
         <v>2025</v>
       </c>
       <c r="C9" s="10" t="n">
@@ -5074,22 +5464,22 @@
       <c r="E9" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="F9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Cost of Sales</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="20" t="n">
         <v>2021</v>
       </c>
       <c r="C10" s="10" t="n">
@@ -5101,22 +5491,22 @@
       <c r="E10" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="F10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Cost of Sales</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n">
+      <c r="B11" s="20" t="n">
         <v>2022</v>
       </c>
       <c r="C11" s="10" t="n">
@@ -5128,22 +5518,22 @@
       <c r="E11" s="10" t="n">
         <v>77</v>
       </c>
-      <c r="F11" s="18" t="n">
+      <c r="F11" s="21" t="n">
         <v>0.0009364092959904658</v>
       </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>Cost of Sales</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
+      <c r="B12" s="20" t="n">
         <v>2023</v>
       </c>
       <c r="C12" s="10" t="n">
@@ -5155,22 +5545,22 @@
       <c r="E12" s="10" t="n">
         <v>92</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="21" t="n">
         <v>0.001183492847586704</v>
       </c>
-      <c r="G12" s="19" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>Cost of Sales</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n">
+      <c r="B13" s="20" t="n">
         <v>2024</v>
       </c>
       <c r="C13" s="10" t="n">
@@ -5182,22 +5572,22 @@
       <c r="E13" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="19" t="inlineStr">
+      <c r="F13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>Cost of Sales</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B14" s="20" t="n">
         <v>2025</v>
       </c>
       <c r="C14" s="10" t="n">
@@ -5209,22 +5599,22 @@
       <c r="E14" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="19" t="inlineStr">
+      <c r="F14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n">
+      <c r="B15" s="20" t="n">
         <v>2021</v>
       </c>
       <c r="C15" s="10" t="n">
@@ -5236,22 +5626,22 @@
       <c r="E15" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="19" t="inlineStr">
+      <c r="F15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B16" s="17" t="n">
+      <c r="B16" s="20" t="n">
         <v>2022</v>
       </c>
       <c r="C16" s="10" t="n">
@@ -5263,22 +5653,22 @@
       <c r="E16" s="10" t="n">
         <v>-77</v>
       </c>
-      <c r="F16" s="18" t="n">
+      <c r="F16" s="21" t="n">
         <v>-0.002863411550332825</v>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B17" s="17" t="n">
+      <c r="B17" s="20" t="n">
         <v>2023</v>
       </c>
       <c r="C17" s="10" t="n">
@@ -5290,22 +5680,22 @@
       <c r="E17" s="10" t="n">
         <v>-92</v>
       </c>
-      <c r="F17" s="18" t="n">
+      <c r="F17" s="21" t="n">
         <v>-0.003100148267960642</v>
       </c>
-      <c r="G17" s="19" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B18" s="17" t="n">
+      <c r="B18" s="20" t="n">
         <v>2024</v>
       </c>
       <c r="C18" s="10" t="n">
@@ -5317,22 +5707,22 @@
       <c r="E18" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="F18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B19" s="17" t="n">
+      <c r="B19" s="20" t="n">
         <v>2025</v>
       </c>
       <c r="C19" s="10" t="n">
@@ -5344,22 +5734,22 @@
       <c r="E19" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="F19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>SG&amp;A</t>
         </is>
       </c>
-      <c r="B20" s="17" t="n">
+      <c r="B20" s="20" t="n">
         <v>2021</v>
       </c>
       <c r="C20" s="10" t="n">
@@ -5371,22 +5761,22 @@
       <c r="E20" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="F20" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>SG&amp;A</t>
         </is>
       </c>
-      <c r="B21" s="17" t="n">
+      <c r="B21" s="20" t="n">
         <v>2022</v>
       </c>
       <c r="C21" s="10" t="n">
@@ -5398,22 +5788,22 @@
       <c r="E21" s="10" t="n">
         <v>-77</v>
       </c>
-      <c r="F21" s="18" t="n">
+      <c r="F21" s="21" t="n">
         <v>-0.003727369542066028</v>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>SG&amp;A</t>
         </is>
       </c>
-      <c r="B22" s="17" t="n">
+      <c r="B22" s="20" t="n">
         <v>2023</v>
       </c>
       <c r="C22" s="10" t="n">
@@ -5425,22 +5815,22 @@
       <c r="E22" s="10" t="n">
         <v>-92</v>
       </c>
-      <c r="F22" s="18" t="n">
+      <c r="F22" s="21" t="n">
         <v>-0.004268349262317899</v>
       </c>
-      <c r="G22" s="19" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>SG&amp;A</t>
         </is>
       </c>
-      <c r="B23" s="17" t="n">
+      <c r="B23" s="20" t="n">
         <v>2024</v>
       </c>
       <c r="C23" s="10" t="n">
@@ -5452,22 +5842,22 @@
       <c r="E23" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="19" t="inlineStr">
+      <c r="F23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>SG&amp;A</t>
         </is>
       </c>
-      <c r="B24" s="17" t="n">
+      <c r="B24" s="20" t="n">
         <v>2025</v>
       </c>
       <c r="C24" s="10" t="n">
@@ -5479,10 +5869,10 @@
       <c r="E24" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F24" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="19" t="inlineStr">
+      <c r="F24" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -5521,7 +5911,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>The only year of quarterly granularity in the registered source set. Grounds the seasonal-liquidity-stress overlay's 50% haircut (Q1 trough vs. Q4/year-end = 52.6%).</t>
         </is>
@@ -5550,7 +5940,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>2025-02-01</t>
         </is>
@@ -5558,19 +5948,19 @@
       <c r="B5" s="10" t="n">
         <v>4762</v>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>0000027419-25-000018</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>FY2024 Year-End</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
@@ -5578,19 +5968,19 @@
       <c r="B6" s="10" t="n">
         <v>2887</v>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>0000027419-25-000101</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>FY2025 Q1 (trough)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
@@ -5598,19 +5988,19 @@
       <c r="B7" s="10" t="n">
         <v>4341</v>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>0000027419-25-000118</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>FY2025 Q2</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>2025-11-01</t>
         </is>
@@ -5618,19 +6008,19 @@
       <c r="B8" s="10" t="n">
         <v>3822</v>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>0000027419-25-000126</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>FY2025 Q3</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>2026-01-31</t>
         </is>
@@ -5638,12 +6028,12 @@
       <c r="B9" s="10" t="n">
         <v>5488</v>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>0000027419-26-000016</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>FY2025 Q4/Year-End</t>
         </is>
@@ -5655,7 +6045,7 @@
           <t>Trough / Year-End Ratio</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="23" t="n">
         <v>0.5260568513119533</v>
       </c>
     </row>
@@ -5713,12 +6103,12 @@
           <t>Scenario Selector</t>
         </is>
       </c>
-      <c r="C2" s="21" t="inlineStr">
+      <c r="C2" s="24" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="D2" s="18" t="inlineStr">
         <is>
           <t>&lt;- choose Base / Upside / Downside; drives Sheets 7-11 live</t>
         </is>
@@ -5834,49 +6224,49 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D5" s="22" t="n">
+      <c r="D5" s="25" t="n">
         <v>0.01</v>
       </c>
-      <c r="E5" s="22" t="n">
+      <c r="E5" s="25" t="n">
         <v>0.01</v>
       </c>
-      <c r="F5" s="22" t="n">
+      <c r="F5" s="25" t="n">
         <v>0.01</v>
       </c>
-      <c r="G5" s="22" t="n">
+      <c r="G5" s="25" t="n">
         <v>0.01</v>
       </c>
-      <c r="H5" s="22" t="n">
+      <c r="H5" s="25" t="n">
         <v>0.01</v>
       </c>
-      <c r="J5" s="22" t="n">
+      <c r="J5" s="25" t="n">
         <v>0.03</v>
       </c>
-      <c r="K5" s="22" t="n">
+      <c r="K5" s="25" t="n">
         <v>0.03</v>
       </c>
-      <c r="L5" s="22" t="n">
+      <c r="L5" s="25" t="n">
         <v>0.03</v>
       </c>
-      <c r="M5" s="22" t="n">
+      <c r="M5" s="25" t="n">
         <v>0.03</v>
       </c>
-      <c r="N5" s="22" t="n">
+      <c r="N5" s="25" t="n">
         <v>0.03</v>
       </c>
-      <c r="P5" s="22" t="n">
+      <c r="P5" s="25" t="n">
         <v>-0.025</v>
       </c>
-      <c r="Q5" s="22" t="n">
+      <c r="Q5" s="25" t="n">
         <v>-0.025</v>
       </c>
-      <c r="R5" s="22" t="n">
+      <c r="R5" s="25" t="n">
         <v>-0.025</v>
       </c>
-      <c r="S5" s="22" t="n">
+      <c r="S5" s="25" t="n">
         <v>-0.025</v>
       </c>
-      <c r="T5" s="22" t="n">
+      <c r="T5" s="25" t="n">
         <v>-0.025</v>
       </c>
     </row>
@@ -5896,49 +6286,49 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D6" s="22" t="n">
+      <c r="D6" s="25" t="n">
         <v>0.2793</v>
       </c>
-      <c r="E6" s="22" t="n">
+      <c r="E6" s="25" t="n">
         <v>0.27947</v>
       </c>
-      <c r="F6" s="22" t="n">
+      <c r="F6" s="25" t="n">
         <v>0.27965</v>
       </c>
-      <c r="G6" s="22" t="n">
+      <c r="G6" s="25" t="n">
         <v>0.27983</v>
       </c>
-      <c r="H6" s="22" t="n">
+      <c r="H6" s="25" t="n">
         <v>0.28</v>
       </c>
-      <c r="J6" s="22" t="n">
+      <c r="J6" s="25" t="n">
         <v>0.2793</v>
       </c>
-      <c r="K6" s="22" t="n">
+      <c r="K6" s="25" t="n">
         <v>0.28148</v>
       </c>
-      <c r="L6" s="22" t="n">
+      <c r="L6" s="25" t="n">
         <v>0.28365</v>
       </c>
-      <c r="M6" s="22" t="n">
+      <c r="M6" s="25" t="n">
         <v>0.28582</v>
       </c>
-      <c r="N6" s="22" t="n">
+      <c r="N6" s="25" t="n">
         <v>0.288</v>
       </c>
-      <c r="P6" s="22" t="n">
+      <c r="P6" s="25" t="n">
         <v>0.2793</v>
       </c>
-      <c r="Q6" s="22" t="n">
+      <c r="Q6" s="25" t="n">
         <v>0.27523</v>
       </c>
-      <c r="R6" s="22" t="n">
+      <c r="R6" s="25" t="n">
         <v>0.27115</v>
       </c>
-      <c r="S6" s="22" t="n">
+      <c r="S6" s="25" t="n">
         <v>0.26707</v>
       </c>
-      <c r="T6" s="22" t="n">
+      <c r="T6" s="25" t="n">
         <v>0.263</v>
       </c>
     </row>
@@ -5958,49 +6348,49 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="25" t="n">
         <v>0.2055</v>
       </c>
-      <c r="E7" s="22" t="n">
+      <c r="E7" s="25" t="n">
         <v>0.2055</v>
       </c>
-      <c r="F7" s="22" t="n">
+      <c r="F7" s="25" t="n">
         <v>0.2055</v>
       </c>
-      <c r="G7" s="22" t="n">
+      <c r="G7" s="25" t="n">
         <v>0.2055</v>
       </c>
-      <c r="H7" s="22" t="n">
+      <c r="H7" s="25" t="n">
         <v>0.2055</v>
       </c>
-      <c r="J7" s="22" t="n">
+      <c r="J7" s="25" t="n">
         <v>0.2055</v>
       </c>
-      <c r="K7" s="22" t="n">
+      <c r="K7" s="25" t="n">
         <v>0.20363</v>
       </c>
-      <c r="L7" s="22" t="n">
+      <c r="L7" s="25" t="n">
         <v>0.20175</v>
       </c>
-      <c r="M7" s="22" t="n">
+      <c r="M7" s="25" t="n">
         <v>0.19988</v>
       </c>
-      <c r="N7" s="22" t="n">
+      <c r="N7" s="25" t="n">
         <v>0.198</v>
       </c>
-      <c r="P7" s="22" t="n">
+      <c r="P7" s="25" t="n">
         <v>0.2055</v>
       </c>
-      <c r="Q7" s="22" t="n">
+      <c r="Q7" s="25" t="n">
         <v>0.20738</v>
       </c>
-      <c r="R7" s="22" t="n">
+      <c r="R7" s="25" t="n">
         <v>0.20925</v>
       </c>
-      <c r="S7" s="22" t="n">
+      <c r="S7" s="25" t="n">
         <v>0.21113</v>
       </c>
-      <c r="T7" s="22" t="n">
+      <c r="T7" s="25" t="n">
         <v>0.213</v>
       </c>
     </row>
@@ -6020,49 +6410,49 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="25" t="n">
         <v>0.02578</v>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="E8" s="25" t="n">
         <v>0.02655</v>
       </c>
-      <c r="F8" s="22" t="n">
+      <c r="F8" s="25" t="n">
         <v>0.02732</v>
       </c>
-      <c r="G8" s="22" t="n">
+      <c r="G8" s="25" t="n">
         <v>0.0281</v>
       </c>
-      <c r="H8" s="22" t="n">
+      <c r="H8" s="25" t="n">
         <v>0.02888</v>
       </c>
-      <c r="J8" s="22" t="n">
+      <c r="J8" s="25" t="n">
         <v>0.02678</v>
       </c>
-      <c r="K8" s="22" t="n">
+      <c r="K8" s="25" t="n">
         <v>0.02755</v>
       </c>
-      <c r="L8" s="22" t="n">
+      <c r="L8" s="25" t="n">
         <v>0.02833</v>
       </c>
-      <c r="M8" s="22" t="n">
+      <c r="M8" s="25" t="n">
         <v>0.0291</v>
       </c>
-      <c r="N8" s="22" t="n">
+      <c r="N8" s="25" t="n">
         <v>0.02988</v>
       </c>
-      <c r="P8" s="22" t="n">
+      <c r="P8" s="25" t="n">
         <v>0.02478</v>
       </c>
-      <c r="Q8" s="22" t="n">
+      <c r="Q8" s="25" t="n">
         <v>0.02555</v>
       </c>
-      <c r="R8" s="22" t="n">
+      <c r="R8" s="25" t="n">
         <v>0.02632</v>
       </c>
-      <c r="S8" s="22" t="n">
+      <c r="S8" s="25" t="n">
         <v>0.0271</v>
       </c>
-      <c r="T8" s="22" t="n">
+      <c r="T8" s="25" t="n">
         <v>0.02788</v>
       </c>
     </row>
@@ -6082,49 +6472,49 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="25" t="n">
         <v>0.222</v>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="E9" s="25" t="n">
         <v>0.222</v>
       </c>
-      <c r="F9" s="22" t="n">
+      <c r="F9" s="25" t="n">
         <v>0.222</v>
       </c>
-      <c r="G9" s="22" t="n">
+      <c r="G9" s="25" t="n">
         <v>0.222</v>
       </c>
-      <c r="H9" s="22" t="n">
+      <c r="H9" s="25" t="n">
         <v>0.222</v>
       </c>
-      <c r="J9" s="22" t="n">
+      <c r="J9" s="25" t="n">
         <v>0.215</v>
       </c>
-      <c r="K9" s="22" t="n">
+      <c r="K9" s="25" t="n">
         <v>0.215</v>
       </c>
-      <c r="L9" s="22" t="n">
+      <c r="L9" s="25" t="n">
         <v>0.215</v>
       </c>
-      <c r="M9" s="22" t="n">
+      <c r="M9" s="25" t="n">
         <v>0.215</v>
       </c>
-      <c r="N9" s="22" t="n">
+      <c r="N9" s="25" t="n">
         <v>0.215</v>
       </c>
-      <c r="P9" s="22" t="n">
+      <c r="P9" s="25" t="n">
         <v>0.23</v>
       </c>
-      <c r="Q9" s="22" t="n">
+      <c r="Q9" s="25" t="n">
         <v>0.23</v>
       </c>
-      <c r="R9" s="22" t="n">
+      <c r="R9" s="25" t="n">
         <v>0.23</v>
       </c>
-      <c r="S9" s="22" t="n">
+      <c r="S9" s="25" t="n">
         <v>0.23</v>
       </c>
-      <c r="T9" s="22" t="n">
+      <c r="T9" s="25" t="n">
         <v>0.23</v>
       </c>
     </row>
@@ -6144,49 +6534,49 @@
           <t>$M</t>
         </is>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="26" t="n">
         <v>95</v>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E10" s="26" t="n">
         <v>95</v>
       </c>
-      <c r="F10" s="23" t="n">
+      <c r="F10" s="26" t="n">
         <v>95</v>
       </c>
-      <c r="G10" s="23" t="n">
+      <c r="G10" s="26" t="n">
         <v>95</v>
       </c>
-      <c r="H10" s="23" t="n">
+      <c r="H10" s="26" t="n">
         <v>95</v>
       </c>
-      <c r="J10" s="23" t="n">
+      <c r="J10" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="K10" s="23" t="n">
+      <c r="K10" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="L10" s="23" t="n">
+      <c r="L10" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="M10" s="23" t="n">
+      <c r="M10" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="N10" s="23" t="n">
+      <c r="N10" s="26" t="n">
         <v>100</v>
       </c>
-      <c r="P10" s="23" t="n">
+      <c r="P10" s="26" t="n">
         <v>80</v>
       </c>
-      <c r="Q10" s="23" t="n">
+      <c r="Q10" s="26" t="n">
         <v>80</v>
       </c>
-      <c r="R10" s="23" t="n">
+      <c r="R10" s="26" t="n">
         <v>80</v>
       </c>
-      <c r="S10" s="23" t="n">
+      <c r="S10" s="26" t="n">
         <v>80</v>
       </c>
-      <c r="T10" s="23" t="n">
+      <c r="T10" s="26" t="n">
         <v>80</v>
       </c>
     </row>
@@ -6206,49 +6596,49 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="25" t="n">
         <v>-0.005</v>
       </c>
-      <c r="E11" s="22" t="n">
+      <c r="E11" s="25" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F11" s="22" t="n">
+      <c r="F11" s="25" t="n">
         <v>-0.005</v>
       </c>
-      <c r="G11" s="22" t="n">
+      <c r="G11" s="25" t="n">
         <v>-0.005</v>
       </c>
-      <c r="H11" s="22" t="n">
+      <c r="H11" s="25" t="n">
         <v>-0.005</v>
       </c>
-      <c r="J11" s="22" t="n">
+      <c r="J11" s="25" t="n">
         <v>-0.015</v>
       </c>
-      <c r="K11" s="22" t="n">
+      <c r="K11" s="25" t="n">
         <v>-0.015</v>
       </c>
-      <c r="L11" s="22" t="n">
+      <c r="L11" s="25" t="n">
         <v>-0.015</v>
       </c>
-      <c r="M11" s="22" t="n">
+      <c r="M11" s="25" t="n">
         <v>-0.015</v>
       </c>
-      <c r="N11" s="22" t="n">
+      <c r="N11" s="25" t="n">
         <v>-0.015</v>
       </c>
-      <c r="P11" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="22" t="n">
+      <c r="P11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6268,49 +6658,49 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="25" t="n">
         <v>0.031</v>
       </c>
-      <c r="E12" s="22" t="n">
+      <c r="E12" s="25" t="n">
         <v>0.031</v>
       </c>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="25" t="n">
         <v>0.031</v>
       </c>
-      <c r="G12" s="22" t="n">
+      <c r="G12" s="25" t="n">
         <v>0.031</v>
       </c>
-      <c r="H12" s="22" t="n">
+      <c r="H12" s="25" t="n">
         <v>0.031</v>
       </c>
-      <c r="J12" s="22" t="n">
+      <c r="J12" s="25" t="n">
         <v>0.029</v>
       </c>
-      <c r="K12" s="22" t="n">
+      <c r="K12" s="25" t="n">
         <v>0.029</v>
       </c>
-      <c r="L12" s="22" t="n">
+      <c r="L12" s="25" t="n">
         <v>0.029</v>
       </c>
-      <c r="M12" s="22" t="n">
+      <c r="M12" s="25" t="n">
         <v>0.029</v>
       </c>
-      <c r="N12" s="22" t="n">
+      <c r="N12" s="25" t="n">
         <v>0.029</v>
       </c>
-      <c r="P12" s="22" t="n">
+      <c r="P12" s="25" t="n">
         <v>0.034</v>
       </c>
-      <c r="Q12" s="22" t="n">
+      <c r="Q12" s="25" t="n">
         <v>0.034</v>
       </c>
-      <c r="R12" s="22" t="n">
+      <c r="R12" s="25" t="n">
         <v>0.034</v>
       </c>
-      <c r="S12" s="22" t="n">
+      <c r="S12" s="25" t="n">
         <v>0.034</v>
       </c>
-      <c r="T12" s="22" t="n">
+      <c r="T12" s="25" t="n">
         <v>0.034</v>
       </c>
     </row>
@@ -6330,49 +6720,49 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="25" t="n">
         <v>0.036</v>
       </c>
-      <c r="E13" s="22" t="n">
+      <c r="E13" s="25" t="n">
         <v>0.036</v>
       </c>
-      <c r="F13" s="22" t="n">
+      <c r="F13" s="25" t="n">
         <v>0.036</v>
       </c>
-      <c r="G13" s="22" t="n">
+      <c r="G13" s="25" t="n">
         <v>0.036</v>
       </c>
-      <c r="H13" s="22" t="n">
+      <c r="H13" s="25" t="n">
         <v>0.036</v>
       </c>
-      <c r="J13" s="22" t="n">
+      <c r="J13" s="25" t="n">
         <v>0.043</v>
       </c>
-      <c r="K13" s="22" t="n">
+      <c r="K13" s="25" t="n">
         <v>0.043</v>
       </c>
-      <c r="L13" s="22" t="n">
+      <c r="L13" s="25" t="n">
         <v>0.043</v>
       </c>
-      <c r="M13" s="22" t="n">
+      <c r="M13" s="25" t="n">
         <v>0.043</v>
       </c>
-      <c r="N13" s="22" t="n">
+      <c r="N13" s="25" t="n">
         <v>0.043</v>
       </c>
-      <c r="P13" s="22" t="n">
+      <c r="P13" s="25" t="n">
         <v>0.028</v>
       </c>
-      <c r="Q13" s="22" t="n">
+      <c r="Q13" s="25" t="n">
         <v>0.028</v>
       </c>
-      <c r="R13" s="22" t="n">
+      <c r="R13" s="25" t="n">
         <v>0.028</v>
       </c>
-      <c r="S13" s="22" t="n">
+      <c r="S13" s="25" t="n">
         <v>0.028</v>
       </c>
-      <c r="T13" s="22" t="n">
+      <c r="T13" s="25" t="n">
         <v>0.028</v>
       </c>
     </row>
@@ -6392,49 +6782,49 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D14" s="22" t="n">
+      <c r="D14" s="25" t="n">
         <v>0.03116</v>
       </c>
-      <c r="E14" s="22" t="n">
+      <c r="E14" s="25" t="n">
         <v>0.03240000000000001</v>
       </c>
-      <c r="F14" s="22" t="n">
+      <c r="F14" s="25" t="n">
         <v>0.03365</v>
       </c>
-      <c r="G14" s="22" t="n">
+      <c r="G14" s="25" t="n">
         <v>0.0349</v>
       </c>
-      <c r="H14" s="22" t="n">
+      <c r="H14" s="25" t="n">
         <v>0.03614</v>
       </c>
-      <c r="J14" s="22" t="n">
+      <c r="J14" s="25" t="n">
         <v>0.03166</v>
       </c>
-      <c r="K14" s="22" t="n">
+      <c r="K14" s="25" t="n">
         <v>0.0329</v>
       </c>
-      <c r="L14" s="22" t="n">
+      <c r="L14" s="25" t="n">
         <v>0.03415</v>
       </c>
-      <c r="M14" s="22" t="n">
+      <c r="M14" s="25" t="n">
         <v>0.0354</v>
       </c>
-      <c r="N14" s="22" t="n">
+      <c r="N14" s="25" t="n">
         <v>0.03664</v>
       </c>
-      <c r="P14" s="22" t="n">
+      <c r="P14" s="25" t="n">
         <v>0.03066</v>
       </c>
-      <c r="Q14" s="22" t="n">
+      <c r="Q14" s="25" t="n">
         <v>0.0319</v>
       </c>
-      <c r="R14" s="22" t="n">
+      <c r="R14" s="25" t="n">
         <v>0.03315</v>
       </c>
-      <c r="S14" s="22" t="n">
+      <c r="S14" s="25" t="n">
         <v>0.0344</v>
       </c>
-      <c r="T14" s="22" t="n">
+      <c r="T14" s="25" t="n">
         <v>0.03564</v>
       </c>
     </row>
@@ -6454,49 +6844,49 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D15" s="22" t="n">
+      <c r="D15" s="25" t="n">
         <v>0.118</v>
       </c>
-      <c r="E15" s="22" t="n">
+      <c r="E15" s="25" t="n">
         <v>0.118</v>
       </c>
-      <c r="F15" s="22" t="n">
+      <c r="F15" s="25" t="n">
         <v>0.118</v>
       </c>
-      <c r="G15" s="22" t="n">
+      <c r="G15" s="25" t="n">
         <v>0.118</v>
       </c>
-      <c r="H15" s="22" t="n">
+      <c r="H15" s="25" t="n">
         <v>0.118</v>
       </c>
-      <c r="J15" s="22" t="n">
+      <c r="J15" s="25" t="n">
         <v>0.11</v>
       </c>
-      <c r="K15" s="22" t="n">
+      <c r="K15" s="25" t="n">
         <v>0.11</v>
       </c>
-      <c r="L15" s="22" t="n">
+      <c r="L15" s="25" t="n">
         <v>0.11</v>
       </c>
-      <c r="M15" s="22" t="n">
+      <c r="M15" s="25" t="n">
         <v>0.11</v>
       </c>
-      <c r="N15" s="22" t="n">
+      <c r="N15" s="25" t="n">
         <v>0.11</v>
       </c>
-      <c r="P15" s="22" t="n">
+      <c r="P15" s="25" t="n">
         <v>0.128</v>
       </c>
-      <c r="Q15" s="22" t="n">
+      <c r="Q15" s="25" t="n">
         <v>0.128</v>
       </c>
-      <c r="R15" s="22" t="n">
+      <c r="R15" s="25" t="n">
         <v>0.128</v>
       </c>
-      <c r="S15" s="22" t="n">
+      <c r="S15" s="25" t="n">
         <v>0.128</v>
       </c>
-      <c r="T15" s="22" t="n">
+      <c r="T15" s="25" t="n">
         <v>0.128</v>
       </c>
     </row>
@@ -6516,49 +6906,49 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D16" s="22" t="n">
+      <c r="D16" s="25" t="n">
         <v>0.167</v>
       </c>
-      <c r="E16" s="22" t="n">
+      <c r="E16" s="25" t="n">
         <v>0.167</v>
       </c>
-      <c r="F16" s="22" t="n">
+      <c r="F16" s="25" t="n">
         <v>0.167</v>
       </c>
-      <c r="G16" s="22" t="n">
+      <c r="G16" s="25" t="n">
         <v>0.167</v>
       </c>
-      <c r="H16" s="22" t="n">
+      <c r="H16" s="25" t="n">
         <v>0.167</v>
       </c>
-      <c r="J16" s="22" t="n">
+      <c r="J16" s="25" t="n">
         <v>0.175</v>
       </c>
-      <c r="K16" s="22" t="n">
+      <c r="K16" s="25" t="n">
         <v>0.175</v>
       </c>
-      <c r="L16" s="22" t="n">
+      <c r="L16" s="25" t="n">
         <v>0.175</v>
       </c>
-      <c r="M16" s="22" t="n">
+      <c r="M16" s="25" t="n">
         <v>0.175</v>
       </c>
-      <c r="N16" s="22" t="n">
+      <c r="N16" s="25" t="n">
         <v>0.175</v>
       </c>
-      <c r="P16" s="22" t="n">
+      <c r="P16" s="25" t="n">
         <v>0.155</v>
       </c>
-      <c r="Q16" s="22" t="n">
+      <c r="Q16" s="25" t="n">
         <v>0.155</v>
       </c>
-      <c r="R16" s="22" t="n">
+      <c r="R16" s="25" t="n">
         <v>0.155</v>
       </c>
-      <c r="S16" s="22" t="n">
+      <c r="S16" s="25" t="n">
         <v>0.155</v>
       </c>
-      <c r="T16" s="22" t="n">
+      <c r="T16" s="25" t="n">
         <v>0.155</v>
       </c>
     </row>
@@ -6578,49 +6968,49 @@
           <t>$M</t>
         </is>
       </c>
-      <c r="D17" s="23" t="n">
+      <c r="D17" s="26" t="n">
         <v>150</v>
       </c>
-      <c r="E17" s="23" t="n">
+      <c r="E17" s="26" t="n">
         <v>150</v>
       </c>
-      <c r="F17" s="23" t="n">
+      <c r="F17" s="26" t="n">
         <v>150</v>
       </c>
-      <c r="G17" s="23" t="n">
+      <c r="G17" s="26" t="n">
         <v>150</v>
       </c>
-      <c r="H17" s="23" t="n">
+      <c r="H17" s="26" t="n">
         <v>150</v>
       </c>
-      <c r="J17" s="23" t="n">
+      <c r="J17" s="26" t="n">
         <v>250</v>
       </c>
-      <c r="K17" s="23" t="n">
+      <c r="K17" s="26" t="n">
         <v>250</v>
       </c>
-      <c r="L17" s="23" t="n">
+      <c r="L17" s="26" t="n">
         <v>250</v>
       </c>
-      <c r="M17" s="23" t="n">
+      <c r="M17" s="26" t="n">
         <v>250</v>
       </c>
-      <c r="N17" s="23" t="n">
+      <c r="N17" s="26" t="n">
         <v>250</v>
       </c>
-      <c r="P17" s="23" t="n">
+      <c r="P17" s="26" t="n">
         <v>50</v>
       </c>
-      <c r="Q17" s="23" t="n">
+      <c r="Q17" s="26" t="n">
         <v>50</v>
       </c>
-      <c r="R17" s="23" t="n">
+      <c r="R17" s="26" t="n">
         <v>50</v>
       </c>
-      <c r="S17" s="23" t="n">
+      <c r="S17" s="26" t="n">
         <v>50</v>
       </c>
-      <c r="T17" s="23" t="n">
+      <c r="T17" s="26" t="n">
         <v>50</v>
       </c>
     </row>
@@ -6640,49 +7030,49 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D18" s="22" t="n">
+      <c r="D18" s="25" t="n">
         <v>0.02</v>
       </c>
-      <c r="E18" s="22" t="n">
+      <c r="E18" s="25" t="n">
         <v>0.02</v>
       </c>
-      <c r="F18" s="22" t="n">
+      <c r="F18" s="25" t="n">
         <v>0.02</v>
       </c>
-      <c r="G18" s="22" t="n">
+      <c r="G18" s="25" t="n">
         <v>0.02</v>
       </c>
-      <c r="H18" s="22" t="n">
+      <c r="H18" s="25" t="n">
         <v>0.02</v>
       </c>
-      <c r="J18" s="22" t="n">
+      <c r="J18" s="25" t="n">
         <v>0.04</v>
       </c>
-      <c r="K18" s="22" t="n">
+      <c r="K18" s="25" t="n">
         <v>0.04</v>
       </c>
-      <c r="L18" s="22" t="n">
+      <c r="L18" s="25" t="n">
         <v>0.04</v>
       </c>
-      <c r="M18" s="22" t="n">
+      <c r="M18" s="25" t="n">
         <v>0.04</v>
       </c>
-      <c r="N18" s="22" t="n">
+      <c r="N18" s="25" t="n">
         <v>0.04</v>
       </c>
-      <c r="P18" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" s="22" t="n">
+      <c r="P18" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6702,49 +7092,49 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D19" s="22" t="n">
+      <c r="D19" s="25" t="n">
         <v>0.4</v>
       </c>
-      <c r="E19" s="22" t="n">
+      <c r="E19" s="25" t="n">
         <v>0.4</v>
       </c>
-      <c r="F19" s="22" t="n">
+      <c r="F19" s="25" t="n">
         <v>0.4</v>
       </c>
-      <c r="G19" s="22" t="n">
+      <c r="G19" s="25" t="n">
         <v>0.4</v>
       </c>
-      <c r="H19" s="22" t="n">
+      <c r="H19" s="25" t="n">
         <v>0.4</v>
       </c>
-      <c r="J19" s="22" t="n">
+      <c r="J19" s="25" t="n">
         <v>0.55</v>
       </c>
-      <c r="K19" s="22" t="n">
+      <c r="K19" s="25" t="n">
         <v>0.55</v>
       </c>
-      <c r="L19" s="22" t="n">
+      <c r="L19" s="25" t="n">
         <v>0.55</v>
       </c>
-      <c r="M19" s="22" t="n">
+      <c r="M19" s="25" t="n">
         <v>0.55</v>
       </c>
-      <c r="N19" s="22" t="n">
+      <c r="N19" s="25" t="n">
         <v>0.55</v>
       </c>
-      <c r="P19" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="22" t="n">
+      <c r="P19" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6764,49 +7154,49 @@
           <t>$M</t>
         </is>
       </c>
-      <c r="D20" s="23" t="n">
+      <c r="D20" s="26" t="n">
         <v>700</v>
       </c>
-      <c r="E20" s="23" t="n">
+      <c r="E20" s="26" t="n">
         <v>700</v>
       </c>
-      <c r="F20" s="23" t="n">
+      <c r="F20" s="26" t="n">
         <v>700</v>
       </c>
-      <c r="G20" s="23" t="n">
+      <c r="G20" s="26" t="n">
         <v>700</v>
       </c>
-      <c r="H20" s="23" t="n">
+      <c r="H20" s="26" t="n">
         <v>700</v>
       </c>
-      <c r="J20" s="23" t="n">
+      <c r="J20" s="26" t="n">
         <v>300</v>
       </c>
-      <c r="K20" s="23" t="n">
+      <c r="K20" s="26" t="n">
         <v>300</v>
       </c>
-      <c r="L20" s="23" t="n">
+      <c r="L20" s="26" t="n">
         <v>300</v>
       </c>
-      <c r="M20" s="23" t="n">
+      <c r="M20" s="26" t="n">
         <v>300</v>
       </c>
-      <c r="N20" s="23" t="n">
+      <c r="N20" s="26" t="n">
         <v>300</v>
       </c>
-      <c r="P20" s="23" t="n">
+      <c r="P20" s="26" t="n">
         <v>500</v>
       </c>
-      <c r="Q20" s="23" t="n">
+      <c r="Q20" s="26" t="n">
         <v>500</v>
       </c>
-      <c r="R20" s="23" t="n">
+      <c r="R20" s="26" t="n">
         <v>500</v>
       </c>
-      <c r="S20" s="23" t="n">
+      <c r="S20" s="26" t="n">
         <v>500</v>
       </c>
-      <c r="T20" s="23" t="n">
+      <c r="T20" s="26" t="n">
         <v>500</v>
       </c>
     </row>
@@ -6826,49 +7216,49 @@
           <t>$M</t>
         </is>
       </c>
-      <c r="D21" s="23" t="n">
+      <c r="D21" s="26" t="n">
         <v>700</v>
       </c>
-      <c r="E21" s="23" t="n">
+      <c r="E21" s="26" t="n">
         <v>700</v>
       </c>
-      <c r="F21" s="23" t="n">
+      <c r="F21" s="26" t="n">
         <v>700</v>
       </c>
-      <c r="G21" s="23" t="n">
+      <c r="G21" s="26" t="n">
         <v>700</v>
       </c>
-      <c r="H21" s="23" t="n">
+      <c r="H21" s="26" t="n">
         <v>700</v>
       </c>
-      <c r="J21" s="23" t="n">
+      <c r="J21" s="26" t="n">
         <v>1000</v>
       </c>
-      <c r="K21" s="23" t="n">
+      <c r="K21" s="26" t="n">
         <v>1000</v>
       </c>
-      <c r="L21" s="23" t="n">
+      <c r="L21" s="26" t="n">
         <v>1000</v>
       </c>
-      <c r="M21" s="23" t="n">
+      <c r="M21" s="26" t="n">
         <v>1000</v>
       </c>
-      <c r="N21" s="23" t="n">
+      <c r="N21" s="26" t="n">
         <v>1000</v>
       </c>
-      <c r="P21" s="23" t="n">
+      <c r="P21" s="26" t="n">
         <v>300</v>
       </c>
-      <c r="Q21" s="23" t="n">
+      <c r="Q21" s="26" t="n">
         <v>300</v>
       </c>
-      <c r="R21" s="23" t="n">
+      <c r="R21" s="26" t="n">
         <v>300</v>
       </c>
-      <c r="S21" s="23" t="n">
+      <c r="S21" s="26" t="n">
         <v>300</v>
       </c>
-      <c r="T21" s="23" t="n">
+      <c r="T21" s="26" t="n">
         <v>300</v>
       </c>
     </row>
@@ -6888,49 +7278,49 @@
           <t>$M</t>
         </is>
       </c>
-      <c r="D22" s="23" t="n">
+      <c r="D22" s="26" t="n">
         <v>2113</v>
       </c>
-      <c r="E22" s="23" t="n">
+      <c r="E22" s="26" t="n">
         <v>2113</v>
       </c>
-      <c r="F22" s="23" t="n">
+      <c r="F22" s="26" t="n">
         <v>2113</v>
       </c>
-      <c r="G22" s="23" t="n">
+      <c r="G22" s="26" t="n">
         <v>2113</v>
       </c>
-      <c r="H22" s="23" t="n">
+      <c r="H22" s="26" t="n">
         <v>2113</v>
       </c>
-      <c r="J22" s="23" t="n">
+      <c r="J22" s="26" t="n">
         <v>2113</v>
       </c>
-      <c r="K22" s="23" t="n">
+      <c r="K22" s="26" t="n">
         <v>2113</v>
       </c>
-      <c r="L22" s="23" t="n">
+      <c r="L22" s="26" t="n">
         <v>2113</v>
       </c>
-      <c r="M22" s="23" t="n">
+      <c r="M22" s="26" t="n">
         <v>2113</v>
       </c>
-      <c r="N22" s="23" t="n">
+      <c r="N22" s="26" t="n">
         <v>2113</v>
       </c>
-      <c r="P22" s="23" t="n">
+      <c r="P22" s="26" t="n">
         <v>2113</v>
       </c>
-      <c r="Q22" s="23" t="n">
+      <c r="Q22" s="26" t="n">
         <v>2113</v>
       </c>
-      <c r="R22" s="23" t="n">
+      <c r="R22" s="26" t="n">
         <v>2113</v>
       </c>
-      <c r="S22" s="23" t="n">
+      <c r="S22" s="26" t="n">
         <v>2113</v>
       </c>
-      <c r="T22" s="23" t="n">
+      <c r="T22" s="26" t="n">
         <v>2113</v>
       </c>
     </row>
@@ -6950,49 +7340,49 @@
           <t>%</t>
         </is>
       </c>
-      <c r="D23" s="22" t="n">
+      <c r="D23" s="25" t="n">
         <v>0.03</v>
       </c>
-      <c r="E23" s="22" t="n">
+      <c r="E23" s="25" t="n">
         <v>0.03</v>
       </c>
-      <c r="F23" s="22" t="n">
+      <c r="F23" s="25" t="n">
         <v>0.03</v>
       </c>
-      <c r="G23" s="22" t="n">
+      <c r="G23" s="25" t="n">
         <v>0.03</v>
       </c>
-      <c r="H23" s="22" t="n">
+      <c r="H23" s="25" t="n">
         <v>0.03</v>
       </c>
-      <c r="J23" s="22" t="n">
+      <c r="J23" s="25" t="n">
         <v>0.03</v>
       </c>
-      <c r="K23" s="22" t="n">
+      <c r="K23" s="25" t="n">
         <v>0.03</v>
       </c>
-      <c r="L23" s="22" t="n">
+      <c r="L23" s="25" t="n">
         <v>0.03</v>
       </c>
-      <c r="M23" s="22" t="n">
+      <c r="M23" s="25" t="n">
         <v>0.03</v>
       </c>
-      <c r="N23" s="22" t="n">
+      <c r="N23" s="25" t="n">
         <v>0.03</v>
       </c>
-      <c r="P23" s="22" t="n">
+      <c r="P23" s="25" t="n">
         <v>0.03</v>
       </c>
-      <c r="Q23" s="22" t="n">
+      <c r="Q23" s="25" t="n">
         <v>0.03</v>
       </c>
-      <c r="R23" s="22" t="n">
+      <c r="R23" s="25" t="n">
         <v>0.03</v>
       </c>
-      <c r="S23" s="22" t="n">
+      <c r="S23" s="25" t="n">
         <v>0.03</v>
       </c>
-      <c r="T23" s="22" t="n">
+      <c r="T23" s="25" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -7041,7 +7431,7 @@
           <t>Selected scenario:</t>
         </is>
       </c>
-      <c r="B2" s="24">
+      <c r="B2" s="27">
         <f>'Forecast Assumptions'!$C$2</f>
         <v/>
       </c>
@@ -7167,23 +7557,23 @@
           <t xml:space="preserve">  Gross Margin %</t>
         </is>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="21">
         <f>IF('Forecast Assumptions'!$C$2="Base",'Forecast Assumptions'!D6,IF('Forecast Assumptions'!$C$2="Upside",'Forecast Assumptions'!J6,'Forecast Assumptions'!P6))</f>
         <v/>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="21">
         <f>IF('Forecast Assumptions'!$C$2="Base",'Forecast Assumptions'!E6,IF('Forecast Assumptions'!$C$2="Upside",'Forecast Assumptions'!K6,'Forecast Assumptions'!Q6))</f>
         <v/>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="21">
         <f>IF('Forecast Assumptions'!$C$2="Base",'Forecast Assumptions'!F6,IF('Forecast Assumptions'!$C$2="Upside",'Forecast Assumptions'!L6,'Forecast Assumptions'!R6))</f>
         <v/>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="21">
         <f>IF('Forecast Assumptions'!$C$2="Base",'Forecast Assumptions'!G6,IF('Forecast Assumptions'!$C$2="Upside",'Forecast Assumptions'!M6,'Forecast Assumptions'!S6))</f>
         <v/>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="21">
         <f>IF('Forecast Assumptions'!$C$2="Base",'Forecast Assumptions'!H6,IF('Forecast Assumptions'!$C$2="Upside",'Forecast Assumptions'!N6,'Forecast Assumptions'!T6))</f>
         <v/>
       </c>
@@ -7275,23 +7665,23 @@
           <t xml:space="preserve">  Operating Margin %</t>
         </is>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="21">
         <f>D11/D5</f>
         <v/>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="21">
         <f>E11/E5</f>
         <v/>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="21">
         <f>F11/F5</f>
         <v/>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="21">
         <f>G11/G5</f>
         <v/>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="21">
         <f>H11/H5</f>
         <v/>
       </c>
@@ -7518,23 +7908,23 @@
           <t>Diluted EPS ($)</t>
         </is>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="17">
         <f>D19/D20</f>
         <v/>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="17">
         <f>E19/E20</f>
         <v/>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="17">
         <f>F19/F20</f>
         <v/>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="17">
         <f>G19/G20</f>
         <v/>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="17">
         <f>H19/H20</f>
         <v/>
       </c>
@@ -7579,7 +7969,7 @@
           <t>Selected scenario:</t>
         </is>
       </c>
-      <c r="B2" s="24">
+      <c r="B2" s="27">
         <f>'Forecast Assumptions'!$C$2</f>
         <v/>
       </c>
@@ -7894,23 +8284,23 @@
           <t>Dividend per Share ($)</t>
         </is>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="17">
         <f>4.506145741878841*(1+(IF('Forecast Assumptions'!$C$2="Base",'Forecast Assumptions'!D18,IF('Forecast Assumptions'!$C$2="Upside",'Forecast Assumptions'!J18,'Forecast Assumptions'!P18))))</f>
         <v/>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="17">
         <f>D15*(1+(IF('Forecast Assumptions'!$C$2="Base",'Forecast Assumptions'!E18,IF('Forecast Assumptions'!$C$2="Upside",'Forecast Assumptions'!K18,'Forecast Assumptions'!Q18))))</f>
         <v/>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="17">
         <f>E15*(1+(IF('Forecast Assumptions'!$C$2="Base",'Forecast Assumptions'!F18,IF('Forecast Assumptions'!$C$2="Upside",'Forecast Assumptions'!L18,'Forecast Assumptions'!R18))))</f>
         <v/>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="17">
         <f>F15*(1+(IF('Forecast Assumptions'!$C$2="Base",'Forecast Assumptions'!G18,IF('Forecast Assumptions'!$C$2="Upside",'Forecast Assumptions'!M18,'Forecast Assumptions'!S18))))</f>
         <v/>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="17">
         <f>G15*(1+(IF('Forecast Assumptions'!$C$2="Base",'Forecast Assumptions'!H18,IF('Forecast Assumptions'!$C$2="Upside",'Forecast Assumptions'!N18,'Forecast Assumptions'!T18))))</f>
         <v/>
       </c>
@@ -8173,7 +8563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -8198,7 +8588,7 @@
           <t>Selected scenario:</t>
         </is>
       </c>
-      <c r="B2" s="24">
+      <c r="B2" s="27">
         <f>'Forecast Assumptions'!$C$2</f>
         <v/>
       </c>
@@ -8402,7 +8792,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>DEPLOYABLE CAPACITY</t>
+          <t>Legacy Gross Pre-Discretionary Ceiling (DEPRECATED -- see note below; not an executive KPI)</t>
         </is>
       </c>
       <c r="D11" s="10">
@@ -8429,22 +8819,22 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Cumulative Deployable Capacity</t>
-        </is>
-      </c>
-      <c r="D12" s="19">
+          <t>Legacy Cumulative (DEPRECATED -- see Corrected Capacity Taxonomy below)</t>
+        </is>
+      </c>
+      <c r="D12" s="22">
         <f>"see terminal year (FY2030)"</f>
         <v/>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="22">
         <f>"see terminal year (FY2030)"</f>
         <v/>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="22">
         <f>"see terminal year (FY2030)"</f>
         <v/>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="22">
         <f>"see terminal year (FY2030)"</f>
         <v/>
       </c>
@@ -8459,30 +8849,599 @@
           <t>Funding Warning? (1=YES)</t>
         </is>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="28">
         <f>IF('Cash-Flow Bridge'!D24&lt;D9,1,0)</f>
         <v/>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="28">
         <f>IF('Cash-Flow Bridge'!E24&lt;E9,1,0)</f>
         <v/>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="28">
         <f>IF('Cash-Flow Bridge'!F24&lt;F9,1,0)</f>
         <v/>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="28">
         <f>IF('Cash-Flow Bridge'!G24&lt;G9,1,0)</f>
         <v/>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="28">
         <f>IF('Cash-Flow Bridge'!H24&lt;H9,1,0)</f>
         <v/>
       </c>
     </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>NOTE: the legacy row above is DEPRECATED -- it is a gross, pre-discretionary ceiling (includes carried-forward cash and new borrowing; never subtracts this year's own repurchases). It is preserved, unmodified, for backward compatibility only. The corrected taxonomy below is the executive-facing figure. See docs/investment_capacity_correction_evidence.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>CORRECTED CAPACITY TAXONOMY (live, selected scenario)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Line Item</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>FY2026</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>FY2027</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>FY2028</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>FY2029</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>FY2030</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>A. Operating FCF (= CFO - CapEx)</t>
+        </is>
+      </c>
+      <c r="D19" s="10">
+        <f>'Cash-Flow Bridge'!D13</f>
+        <v/>
+      </c>
+      <c r="E19" s="10">
+        <f>'Cash-Flow Bridge'!E13</f>
+        <v/>
+      </c>
+      <c r="F19" s="10">
+        <f>'Cash-Flow Bridge'!F13</f>
+        <v/>
+      </c>
+      <c r="G19" s="10">
+        <f>'Cash-Flow Bridge'!G13</f>
+        <v/>
+      </c>
+      <c r="H19" s="10">
+        <f>'Cash-Flow Bridge'!H13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>B. Post-Dividend Internal Generation</t>
+        </is>
+      </c>
+      <c r="D20" s="10">
+        <f>D19-'Cash-Flow Bridge'!D16</f>
+        <v/>
+      </c>
+      <c r="E20" s="10">
+        <f>E19-'Cash-Flow Bridge'!E16</f>
+        <v/>
+      </c>
+      <c r="F20" s="10">
+        <f>F19-'Cash-Flow Bridge'!F16</f>
+        <v/>
+      </c>
+      <c r="G20" s="10">
+        <f>G19-'Cash-Flow Bridge'!G16</f>
+        <v/>
+      </c>
+      <c r="H20" s="10">
+        <f>H19-'Cash-Flow Bridge'!H16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Opening Excess Liquidity (stock, = MAX(0, beg. cash - buffer))</t>
+        </is>
+      </c>
+      <c r="D21" s="10">
+        <f>MAX(0,'Cash-Flow Bridge'!D22-D9)</f>
+        <v/>
+      </c>
+      <c r="E21" s="10">
+        <f>MAX(0,'Cash-Flow Bridge'!E22-E9)</f>
+        <v/>
+      </c>
+      <c r="F21" s="10">
+        <f>MAX(0,'Cash-Flow Bridge'!F22-F9)</f>
+        <v/>
+      </c>
+      <c r="G21" s="10">
+        <f>MAX(0,'Cash-Flow Bridge'!G22-G9)</f>
+        <v/>
+      </c>
+      <c r="H21" s="10">
+        <f>MAX(0,'Cash-Flow Bridge'!H22-H9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Mandatory Debt Uses</t>
+        </is>
+      </c>
+      <c r="D22" s="10">
+        <f>'Cash-Flow Bridge'!D20</f>
+        <v/>
+      </c>
+      <c r="E22" s="10">
+        <f>'Cash-Flow Bridge'!E20</f>
+        <v/>
+      </c>
+      <c r="F22" s="10">
+        <f>'Cash-Flow Bridge'!F20</f>
+        <v/>
+      </c>
+      <c r="G22" s="10">
+        <f>'Cash-Flow Bridge'!G20</f>
+        <v/>
+      </c>
+      <c r="H22" s="10">
+        <f>'Cash-Flow Bridge'!H20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>C. Self-Funded Gross Capacity (excl. new borrowing)</t>
+        </is>
+      </c>
+      <c r="D23" s="10">
+        <f>D21+D20-D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="10">
+        <f>E21+E20-E22</f>
+        <v/>
+      </c>
+      <c r="F23" s="10">
+        <f>F21+F20-F22</f>
+        <v/>
+      </c>
+      <c r="G23" s="10">
+        <f>G21+G20-G22</f>
+        <v/>
+      </c>
+      <c r="H23" s="10">
+        <f>H21+H20-H22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>D. Debt-Funded Incremental Capacity (new borrowing)</t>
+        </is>
+      </c>
+      <c r="D24" s="10">
+        <f>'Cash-Flow Bridge'!D19</f>
+        <v/>
+      </c>
+      <c r="E24" s="10">
+        <f>'Cash-Flow Bridge'!E19</f>
+        <v/>
+      </c>
+      <c r="F24" s="10">
+        <f>'Cash-Flow Bridge'!F19</f>
+        <v/>
+      </c>
+      <c r="G24" s="10">
+        <f>'Cash-Flow Bridge'!G19</f>
+        <v/>
+      </c>
+      <c r="H24" s="10">
+        <f>'Cash-Flow Bridge'!H19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>E. TOTAL GROSS FUNDING CAPACITY (C + D)</t>
+        </is>
+      </c>
+      <c r="D25" s="10">
+        <f>D23+D24</f>
+        <v/>
+      </c>
+      <c r="E25" s="10">
+        <f>E23+E24</f>
+        <v/>
+      </c>
+      <c r="F25" s="10">
+        <f>F23+F24</f>
+        <v/>
+      </c>
+      <c r="G25" s="10">
+        <f>G23+G24</f>
+        <v/>
+      </c>
+      <c r="H25" s="10">
+        <f>H23+H24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Share Repurchases</t>
+        </is>
+      </c>
+      <c r="D26" s="10">
+        <f>'Cash-Flow Bridge'!D18</f>
+        <v/>
+      </c>
+      <c r="E26" s="10">
+        <f>'Cash-Flow Bridge'!E18</f>
+        <v/>
+      </c>
+      <c r="F26" s="10">
+        <f>'Cash-Flow Bridge'!F18</f>
+        <v/>
+      </c>
+      <c r="G26" s="10">
+        <f>'Cash-Flow Bridge'!G18</f>
+        <v/>
+      </c>
+      <c r="H26" s="10">
+        <f>'Cash-Flow Bridge'!H18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Strategic Investment (none modeled this round)</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Voluntary Debt Reduction (none modeled this round)</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Other Discretionary Uses (none modeled this round)</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>F. TOTAL DISCRETIONARY DEPLOYMENT</t>
+        </is>
+      </c>
+      <c r="D30" s="10">
+        <f>D26+D27+D28+D29</f>
+        <v/>
+      </c>
+      <c r="E30" s="10">
+        <f>E26+E27+E28+E29</f>
+        <v/>
+      </c>
+      <c r="F30" s="10">
+        <f>F26+F27+F28+F29</f>
+        <v/>
+      </c>
+      <c r="G30" s="10">
+        <f>G26+G27+G28+G29</f>
+        <v/>
+      </c>
+      <c r="H30" s="10">
+        <f>H26+H27+H28+H29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>G. REMAINING DEPLOYABLE HEADROOM (stock, = MAX(0, E - F))</t>
+        </is>
+      </c>
+      <c r="D31" s="10">
+        <f>MAX(0,D25-D30)</f>
+        <v/>
+      </c>
+      <c r="E31" s="10">
+        <f>MAX(0,E25-E30)</f>
+        <v/>
+      </c>
+      <c r="F31" s="10">
+        <f>MAX(0,F25-F30)</f>
+        <v/>
+      </c>
+      <c r="G31" s="10">
+        <f>MAX(0,G25-G30)</f>
+        <v/>
+      </c>
+      <c r="H31" s="10">
+        <f>MAX(0,H25-H30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Ending Excess Liquidity (independent cross-check of G)</t>
+        </is>
+      </c>
+      <c r="D32" s="10">
+        <f>MAX(0,'Cash-Flow Bridge'!D24-D9)</f>
+        <v/>
+      </c>
+      <c r="E32" s="10">
+        <f>MAX(0,'Cash-Flow Bridge'!E24-E9)</f>
+        <v/>
+      </c>
+      <c r="F32" s="10">
+        <f>MAX(0,'Cash-Flow Bridge'!F24-F9)</f>
+        <v/>
+      </c>
+      <c r="G32" s="10">
+        <f>MAX(0,'Cash-Flow Bridge'!G24-G9)</f>
+        <v/>
+      </c>
+      <c r="H32" s="10">
+        <f>MAX(0,'Cash-Flow Bridge'!H24-H9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>Independent proof: Ending Excess Liquidity (from ending cash) equals Remaining Deployable Headroom (from the discretionary-deployment waterfall) for every year -- confirming no dollar is counted in both headroom and deployment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="31" t="inlineStr">
+        <is>
+          <t>CUMULATIVE CAPACITY RECONCILIATION, FY2026-FY2030 (STATIC reference, all scenarios -- from target_cash.capacity_taxonomy; NEVER a sum of per-year ending balances)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>A. Cumulative Self-Funded Generation</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>B. Cumulative Debt-Funded Capacity</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>C. Opening Excess Liquidity (horizon start)</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>D. Cumulative Discretionary Deployment</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>E. Terminal Remaining Headroom</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>Ending Reserve Movement</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>Total Horizon Capacity Accessible (C+A+B)</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>Reconciles To (D+E+Reserve Mvmt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n">
+        <v>3490.8</v>
+      </c>
+      <c r="C38" s="10" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>2313.2</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>2796.3</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>6378.7</v>
+      </c>
+      <c r="G38" s="10" t="n">
+        <v>128.9</v>
+      </c>
+      <c r="H38" s="10" t="n">
+        <v>9303.9</v>
+      </c>
+      <c r="I38" s="10" t="n">
+        <v>9303.9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="n">
+        <v>4776.8</v>
+      </c>
+      <c r="C39" s="10" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>2250.3</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>5377.2</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>2743.5</v>
+      </c>
+      <c r="G39" s="10" t="n">
+        <v>406.4</v>
+      </c>
+      <c r="H39" s="10" t="n">
+        <v>8527.1</v>
+      </c>
+      <c r="I39" s="10" t="n">
+        <v>8527.1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>Downside</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="n">
+        <v>1169.2</v>
+      </c>
+      <c r="C40" s="10" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>2423.2</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>6387.5</v>
+      </c>
+      <c r="G40" s="10" t="n">
+        <v>-295.2</v>
+      </c>
+      <c r="H40" s="10" t="n">
+        <v>6092.3</v>
+      </c>
+      <c r="I40" s="10" t="n">
+        <v>6092.3</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="5">
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A17:H17"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/deliverables/Target_Cash_Flow_Investment_Capacity_Model.xlsx
+++ b/deliverables/Target_Cash_Flow_Investment_Capacity_Model.xlsx
@@ -24,7 +24,7 @@
     <sheet name="Limitations" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Executive Summary'!$A$1:$D$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Executive Summary'!$A$1:$D$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -108,6 +108,11 @@
     </font>
     <font>
       <i val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
       <sz val="9"/>
     </font>
     <font>
@@ -118,11 +123,6 @@
     <font>
       <b val="1"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -190,7 +190,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -222,11 +222,11 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="9" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -331,7 +331,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Executive Summary'!B23</f>
+              <f>'Executive Summary'!B24</f>
             </strRef>
           </tx>
           <spPr>
@@ -341,12 +341,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Executive Summary'!$A$24:$A$26</f>
+              <f>'Executive Summary'!$A$25:$A$27</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Executive Summary'!$B$24:$B$26</f>
+              <f>'Executive Summary'!$B$25:$B$27</f>
             </numRef>
           </val>
         </ser>
@@ -3406,7 +3406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3998,7 +3998,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Corrected Capacity Taxonomy (Milestone 9 correction): 13 named checks</t>
+          <t>Corrected Capacity Taxonomy (Milestone 9 v2 correction): 18 named checks</t>
         </is>
       </c>
     </row>
@@ -4127,7 +4127,7 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>ending_cash_above_buffer_or_flagged</t>
+          <t>debt_funded_capacity_excludes_gross_issuance</t>
         </is>
       </c>
       <c r="B47" s="22" t="n">
@@ -4146,7 +4146,7 @@
     <row r="48">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>headroom_never_negative</t>
+          <t>debt_netting_mutually_exclusive</t>
         </is>
       </c>
       <c r="B48" s="22" t="n">
@@ -4165,7 +4165,7 @@
     <row r="49">
       <c r="A49" s="20" t="inlineStr">
         <is>
-          <t>mandatory_debt_not_double_deducted</t>
+          <t>ending_cash_above_buffer_or_flagged</t>
         </is>
       </c>
       <c r="B49" s="22" t="n">
@@ -4184,7 +4184,7 @@
     <row r="50">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>opening_excess_liquidity_excluded_from_generation</t>
+          <t>forward_reserve_terminal_proxy_documented</t>
         </is>
       </c>
       <c r="B50" s="22" t="n">
@@ -4203,7 +4203,7 @@
     <row r="51">
       <c r="A51" s="20" t="inlineStr">
         <is>
-          <t>operating_fcf_reconciles</t>
+          <t>headroom_deducts_forward_reserve</t>
         </is>
       </c>
       <c r="B51" s="22" t="n">
@@ -4222,7 +4222,7 @@
     <row r="52">
       <c r="A52" s="20" t="inlineStr">
         <is>
-          <t>post_dividend_generation_reconciles</t>
+          <t>headroom_never_negative</t>
         </is>
       </c>
       <c r="B52" s="22" t="n">
@@ -4241,7 +4241,7 @@
     <row r="53">
       <c r="A53" s="20" t="inlineStr">
         <is>
-          <t>repurchases_in_discretionary_deployment</t>
+          <t>mandatory_debt_not_double_deducted</t>
         </is>
       </c>
       <c r="B53" s="22" t="n">
@@ -4260,26 +4260,121 @@
     <row r="54">
       <c r="A54" s="20" t="inlineStr">
         <is>
+          <t>opening_excess_liquidity_excluded_from_generation</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C54" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t>operating_fcf_reconciles</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C55" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="D55" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t>post_dividend_generation_reconciles</t>
+        </is>
+      </c>
+      <c r="B56" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C56" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="D56" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="20" t="inlineStr">
+        <is>
+          <t>repurchases_in_discretionary_deployment</t>
+        </is>
+      </c>
+      <c r="B57" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C57" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="D57" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="20" t="inlineStr">
+        <is>
           <t>scenario_and_cutoff_lineage_complete</t>
         </is>
       </c>
-      <c r="B54" s="22" t="n">
+      <c r="B58" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="C54" s="22" t="n">
+      <c r="C58" s="22" t="n">
         <v>15</v>
       </c>
-      <c r="D54" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL: 147 results, 0 failures (7 further structural/definitional proofs live in tests/unit/test_capacity_taxonomy.py)</t>
+      <c r="D58" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="20" t="inlineStr">
+        <is>
+          <t>self_funded_generation_excludes_opening_liquidity</t>
+        </is>
+      </c>
+      <c r="B59" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C59" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="D59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL: 210 results, 0 failures (7 further structural/definitional proofs live in tests/unit/test_capacity_taxonomy.py)</t>
         </is>
       </c>
     </row>
@@ -4298,7 +4393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -4406,6 +4501,13 @@
       <c r="A16" s="16" t="inlineStr">
         <is>
           <t>- strategic_investment, voluntary_debt_reduction, and other_discretionary_uses in the corrected taxonomy are structural $0 placeholders -- no policy lever for them has been modeled this round, following the same convention already established for management_selected_deployment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>- v2 finance-semantics correction: debt_funded_incremental_capacity previously equaled gross debt proceeds, mislabeling capacity even when the same cash was simultaneously repaid. It is now the NET of proceeds over repayments; the offsetting net_mandatory_debt_service is subtracted from self_funded_capacity_generated, which now excludes opening_excess_liquidity entirely (a stock is never labeled 'generated'). Remaining Deployable Headroom now also deducts a forward debt-repayment reserve, proxied for the terminal FY2030 year since FY2031 is outside the forecast horizon. See docs/investment_capacity_correction_evidence.md.</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4559,151 +4661,167 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Self-Funded Capacity Generated ($M)</t>
+          <t>Opening Excess Liquidity ($M, a STOCK -- never 'generated')</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>6315.02</v>
+        <v>5424.25</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>3941.94</v>
+        <v>2217.5</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>5887.52</v>
+        <v>6157.88</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Debt-Funded Capacity ($M)</t>
+          <t>Self-Funded Capacity Generated ($M)</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>700</v>
+        <v>1590.77</v>
       </c>
       <c r="C13" s="13" t="n">
-        <v>300</v>
+        <v>2024.44</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>500</v>
+        <v>29.64</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Discretionary Deployment ($M)</t>
+          <t>Debt-Funded Capacity ($M, net of repayment)</t>
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>636.3099999999999</v>
+        <v>0</v>
       </c>
       <c r="C14" s="13" t="n">
-        <v>1498.44</v>
+        <v>0</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>Discretionary Deployment ($M)</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>636.3099999999999</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>1498.44</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>Remaining Deployable Headroom ($M)</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B16" s="13" t="n">
         <v>6378.71</v>
       </c>
-      <c r="C15" s="13" t="n">
-        <v>2743.5</v>
-      </c>
-      <c r="D15" s="13" t="n">
+      <c r="C16" s="13" t="n">
+        <v>2043.5</v>
+      </c>
+      <c r="D16" s="13" t="n">
         <v>6387.52</v>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Note: a higher-revenue scenario can show LOWER remaining headroom -- it may be deploying far more into buybacks/deleveraging (Upside), not generating less. See the FY2030 scenario bridges in docs/investment_capacity_correction_evidence.md and Sheet 9.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Implied DCF Value/Share ($)</t>
         </is>
       </c>
-      <c r="B18" s="15" t="n">
+      <c r="B19" s="15" t="n">
         <v>107.29</v>
       </c>
-      <c r="C18" s="15" t="n">
+      <c r="C19" s="15" t="n">
         <v>138.32</v>
       </c>
-      <c r="D18" s="15" t="n">
+      <c r="D19" s="15" t="n">
         <v>61.55</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Key question answered:</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>How much capital can Target safely deploy after funding operations, CapEx, dividends, minimum liquidity, and debt obligations? -- see Sheet 9 (Investment Capacity) for the full FY2026-FY2030 build for the selected scenario.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Remaining Deployable Headroom, FY2030 ($M)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>6378.7</v>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Remaining Deployable Headroom, FY2030 ($M)</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Upside</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2743.5</v>
+        <v>6378.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Upside</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2043.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Downside</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B27" t="n">
         <v>6387.5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8563,7 +8681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -8975,7 +9093,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Opening Excess Liquidity (stock, = MAX(0, beg. cash - buffer))</t>
+          <t>Opening Excess Liquidity (STOCK, = MAX(0, beg. cash - buffer)) -- never labeled 'generated'</t>
         </is>
       </c>
       <c r="D21" s="10">
@@ -9002,446 +9120,595 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Mandatory Debt Uses</t>
+          <t xml:space="preserve">  Gross Debt Proceeds (supporting, transparent)</t>
         </is>
       </c>
       <c r="D22" s="10">
+        <f>'Cash-Flow Bridge'!D19</f>
+        <v/>
+      </c>
+      <c r="E22" s="10">
+        <f>'Cash-Flow Bridge'!E19</f>
+        <v/>
+      </c>
+      <c r="F22" s="10">
+        <f>'Cash-Flow Bridge'!F19</f>
+        <v/>
+      </c>
+      <c r="G22" s="10">
+        <f>'Cash-Flow Bridge'!G19</f>
+        <v/>
+      </c>
+      <c r="H22" s="10">
+        <f>'Cash-Flow Bridge'!H19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Gross Debt Repayments (supporting, transparent)</t>
+        </is>
+      </c>
+      <c r="D23" s="10">
         <f>'Cash-Flow Bridge'!D20</f>
         <v/>
       </c>
-      <c r="E22" s="10">
+      <c r="E23" s="10">
         <f>'Cash-Flow Bridge'!E20</f>
         <v/>
       </c>
-      <c r="F22" s="10">
+      <c r="F23" s="10">
         <f>'Cash-Flow Bridge'!F20</f>
         <v/>
       </c>
-      <c r="G22" s="10">
+      <c r="G23" s="10">
         <f>'Cash-Flow Bridge'!G20</f>
         <v/>
       </c>
-      <c r="H22" s="10">
+      <c r="H23" s="10">
         <f>'Cash-Flow Bridge'!H20</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>C. Self-Funded Gross Capacity (excl. new borrowing)</t>
-        </is>
-      </c>
-      <c r="D23" s="10">
-        <f>D21+D20-D22</f>
-        <v/>
-      </c>
-      <c r="E23" s="10">
-        <f>E21+E20-E22</f>
-        <v/>
-      </c>
-      <c r="F23" s="10">
-        <f>F21+F20-F22</f>
-        <v/>
-      </c>
-      <c r="G23" s="10">
-        <f>G21+G20-G22</f>
-        <v/>
-      </c>
-      <c r="H23" s="10">
-        <f>H21+H20-H22</f>
-        <v/>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>D. Debt-Funded Incremental Capacity (new borrowing)</t>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Net Mandatory Debt Service (= MAX(0, gross repayments - gross proceeds))</t>
         </is>
       </c>
       <c r="D24" s="10">
-        <f>'Cash-Flow Bridge'!D19</f>
+        <f>MAX(0,D23-D22)</f>
         <v/>
       </c>
       <c r="E24" s="10">
-        <f>'Cash-Flow Bridge'!E19</f>
+        <f>MAX(0,E23-E22)</f>
         <v/>
       </c>
       <c r="F24" s="10">
-        <f>'Cash-Flow Bridge'!F19</f>
+        <f>MAX(0,F23-F22)</f>
         <v/>
       </c>
       <c r="G24" s="10">
-        <f>'Cash-Flow Bridge'!G19</f>
+        <f>MAX(0,G23-G22)</f>
         <v/>
       </c>
       <c r="H24" s="10">
-        <f>'Cash-Flow Bridge'!H19</f>
+        <f>MAX(0,H23-H22)</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>E. TOTAL GROSS FUNDING CAPACITY (C + D)</t>
+          <t>C. Self-Funded Capacity Generated (FLOW, excludes opening liquidity)</t>
         </is>
       </c>
       <c r="D25" s="10">
-        <f>D23+D24</f>
+        <f>D20-D24</f>
         <v/>
       </c>
       <c r="E25" s="10">
-        <f>E23+E24</f>
+        <f>E20-E24</f>
         <v/>
       </c>
       <c r="F25" s="10">
-        <f>F23+F24</f>
+        <f>F20-F24</f>
         <v/>
       </c>
       <c r="G25" s="10">
-        <f>G23+G24</f>
+        <f>G20-G24</f>
         <v/>
       </c>
       <c r="H25" s="10">
-        <f>H23+H24</f>
+        <f>H20-H24</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Share Repurchases</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>D. Debt-Funded Incremental Capacity (= MAX(0, proceeds - repayments); never gross issuance)</t>
         </is>
       </c>
       <c r="D26" s="10">
-        <f>'Cash-Flow Bridge'!D18</f>
+        <f>MAX(0,D22-D23)</f>
         <v/>
       </c>
       <c r="E26" s="10">
-        <f>'Cash-Flow Bridge'!E18</f>
+        <f>MAX(0,E22-E23)</f>
         <v/>
       </c>
       <c r="F26" s="10">
-        <f>'Cash-Flow Bridge'!F18</f>
+        <f>MAX(0,F22-F23)</f>
         <v/>
       </c>
       <c r="G26" s="10">
-        <f>'Cash-Flow Bridge'!G18</f>
+        <f>MAX(0,G22-G23)</f>
         <v/>
       </c>
       <c r="H26" s="10">
-        <f>'Cash-Flow Bridge'!H18</f>
+        <f>MAX(0,H22-H23)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Strategic Investment (none modeled this round)</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="10" t="n">
-        <v>0</v>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>E. TOTAL GROSS FUNDING CAPACITY (Opening Liquidity + C + D)</t>
+        </is>
+      </c>
+      <c r="D27" s="10">
+        <f>D21+D25+D26</f>
+        <v/>
+      </c>
+      <c r="E27" s="10">
+        <f>E21+E25+E26</f>
+        <v/>
+      </c>
+      <c r="F27" s="10">
+        <f>F21+F25+F26</f>
+        <v/>
+      </c>
+      <c r="G27" s="10">
+        <f>G21+G25+G26</f>
+        <v/>
+      </c>
+      <c r="H27" s="10">
+        <f>H21+H25+H26</f>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Voluntary Debt Reduction (none modeled this round)</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="10" t="n">
-        <v>0</v>
+          <t xml:space="preserve">  Share Repurchases</t>
+        </is>
+      </c>
+      <c r="D28" s="10">
+        <f>'Cash-Flow Bridge'!D18</f>
+        <v/>
+      </c>
+      <c r="E28" s="10">
+        <f>'Cash-Flow Bridge'!E18</f>
+        <v/>
+      </c>
+      <c r="F28" s="10">
+        <f>'Cash-Flow Bridge'!F18</f>
+        <v/>
+      </c>
+      <c r="G28" s="10">
+        <f>'Cash-Flow Bridge'!G18</f>
+        <v/>
+      </c>
+      <c r="H28" s="10">
+        <f>'Cash-Flow Bridge'!H18</f>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Strategic Investment (none modeled this round)</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Voluntary Debt Reduction (none modeled this round)</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Other Discretionary Uses (none modeled this round)</t>
         </is>
       </c>
-      <c r="D29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="D31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>F. TOTAL DISCRETIONARY DEPLOYMENT</t>
         </is>
       </c>
-      <c r="D30" s="10">
-        <f>D26+D27+D28+D29</f>
-        <v/>
-      </c>
-      <c r="E30" s="10">
-        <f>E26+E27+E28+E29</f>
-        <v/>
-      </c>
-      <c r="F30" s="10">
-        <f>F26+F27+F28+F29</f>
-        <v/>
-      </c>
-      <c r="G30" s="10">
-        <f>G26+G27+G28+G29</f>
-        <v/>
-      </c>
-      <c r="H30" s="10">
-        <f>H26+H27+H28+H29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>G. REMAINING DEPLOYABLE HEADROOM (stock, = MAX(0, E - F))</t>
-        </is>
-      </c>
-      <c r="D31" s="10">
-        <f>MAX(0,D25-D30)</f>
-        <v/>
-      </c>
-      <c r="E31" s="10">
-        <f>MAX(0,E25-E30)</f>
-        <v/>
-      </c>
-      <c r="F31" s="10">
-        <f>MAX(0,F25-F30)</f>
-        <v/>
-      </c>
-      <c r="G31" s="10">
-        <f>MAX(0,G25-G30)</f>
-        <v/>
-      </c>
-      <c r="H31" s="10">
-        <f>MAX(0,H25-H30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Ending Excess Liquidity (independent cross-check of G)</t>
-        </is>
-      </c>
       <c r="D32" s="10">
+        <f>D28+D29+D30+D31</f>
+        <v/>
+      </c>
+      <c r="E32" s="10">
+        <f>E28+E29+E30+E31</f>
+        <v/>
+      </c>
+      <c r="F32" s="10">
+        <f>F28+F29+F30+F31</f>
+        <v/>
+      </c>
+      <c r="G32" s="10">
+        <f>G28+G29+G30+G31</f>
+        <v/>
+      </c>
+      <c r="H32" s="10">
+        <f>H28+H29+H30+H31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Forward Debt-Repayment Reserve (next year's net debt service; FY2030 is a documented FY2031 proxy)</t>
+        </is>
+      </c>
+      <c r="D33" s="10">
+        <f>E24</f>
+        <v/>
+      </c>
+      <c r="E33" s="10">
+        <f>F24</f>
+        <v/>
+      </c>
+      <c r="F33" s="10">
+        <f>G24</f>
+        <v/>
+      </c>
+      <c r="G33" s="10">
+        <f>H24</f>
+        <v/>
+      </c>
+      <c r="H33" s="10">
+        <f>H24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>G. REMAINING DEPLOYABLE HEADROOM (stock, = MAX(0, E - F - forward reserve))</t>
+        </is>
+      </c>
+      <c r="D34" s="10">
+        <f>MAX(0,D27-D32-D33)</f>
+        <v/>
+      </c>
+      <c r="E34" s="10">
+        <f>MAX(0,E27-E32-E33)</f>
+        <v/>
+      </c>
+      <c r="F34" s="10">
+        <f>MAX(0,F27-F32-F33)</f>
+        <v/>
+      </c>
+      <c r="G34" s="10">
+        <f>MAX(0,G27-G32-G33)</f>
+        <v/>
+      </c>
+      <c r="H34" s="10">
+        <f>MAX(0,H27-H32-H33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Ending Excess Liquidity (independent cross-check: = G + forward reserve)</t>
+        </is>
+      </c>
+      <c r="D35" s="10">
         <f>MAX(0,'Cash-Flow Bridge'!D24-D9)</f>
         <v/>
       </c>
-      <c r="E32" s="10">
+      <c r="E35" s="10">
         <f>MAX(0,'Cash-Flow Bridge'!E24-E9)</f>
         <v/>
       </c>
-      <c r="F32" s="10">
+      <c r="F35" s="10">
         <f>MAX(0,'Cash-Flow Bridge'!F24-F9)</f>
         <v/>
       </c>
-      <c r="G32" s="10">
+      <c r="G35" s="10">
         <f>MAX(0,'Cash-Flow Bridge'!G24-G9)</f>
         <v/>
       </c>
-      <c r="H32" s="10">
+      <c r="H35" s="10">
         <f>MAX(0,'Cash-Flow Bridge'!H24-H9)</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="30" t="inlineStr">
-        <is>
-          <t>Independent proof: Ending Excess Liquidity (from ending cash) equals Remaining Deployable Headroom (from the discretionary-deployment waterfall) for every year -- confirming no dollar is counted in both headroom and deployment.</t>
-        </is>
-      </c>
-    </row>
     <row r="36">
-      <c r="A36" s="31" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>DEPRECATED: Mandatory Debt Uses (v1, = gross repayments, double-subtracted -- see evidence doc)</t>
+        </is>
+      </c>
+      <c r="D36" s="10">
+        <f>D24</f>
+        <v/>
+      </c>
+      <c r="E36" s="10">
+        <f>E24</f>
+        <v/>
+      </c>
+      <c r="F36" s="10">
+        <f>F24</f>
+        <v/>
+      </c>
+      <c r="G36" s="10">
+        <f>G24</f>
+        <v/>
+      </c>
+      <c r="H36" s="10">
+        <f>H24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>DEPRECATED: Self-Funded Gross Capacity (v1-style, includes opening liquidity -- never labeled 'generated')</t>
+        </is>
+      </c>
+      <c r="D37" s="10">
+        <f>D21+D25</f>
+        <v/>
+      </c>
+      <c r="E37" s="10">
+        <f>E21+E25</f>
+        <v/>
+      </c>
+      <c r="F37" s="10">
+        <f>F21+F25</f>
+        <v/>
+      </c>
+      <c r="G37" s="10">
+        <f>G21+G25</f>
+        <v/>
+      </c>
+      <c r="H37" s="10">
+        <f>H21+H25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="30" t="inlineStr">
+        <is>
+          <t>Independent proof: Ending Excess Liquidity (from ending cash) equals Remaining Deployable Headroom PLUS the Forward Debt-Repayment Reserve, for every year -- confirming no dollar is counted in both headroom and deployment/reserve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="31" t="inlineStr">
         <is>
           <t>CUMULATIVE CAPACITY RECONCILIATION, FY2026-FY2030 (STATIC reference, all scenarios -- from target_cash.capacity_taxonomy; NEVER a sum of per-year ending balances)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>A. Cumulative Self-Funded Generation</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>B. Cumulative Debt-Funded Capacity</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>C. Opening Excess Liquidity (horizon start)</t>
         </is>
       </c>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="E42" s="9" t="inlineStr">
         <is>
           <t>D. Cumulative Discretionary Deployment</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F42" s="9" t="inlineStr">
         <is>
           <t>E. Terminal Remaining Headroom</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="G42" s="9" t="inlineStr">
         <is>
           <t>Ending Reserve Movement</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>Terminal Forward Debt-Repayment Reserve (FY2031 proxy)</t>
+        </is>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>Total Horizon Capacity Accessible (C+A+B)</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>Reconciles To (D+E+Reserve Mvmt)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="22" t="inlineStr">
+      <c r="J42" s="9" t="inlineStr">
+        <is>
+          <t>Reconciles To (D+E+Reserve Mvmt+Forward Reserve)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="B38" s="10" t="n">
-        <v>3490.8</v>
-      </c>
-      <c r="C38" s="10" t="n">
-        <v>3500</v>
-      </c>
-      <c r="D38" s="10" t="n">
+      <c r="B43" s="10" t="n">
+        <v>6990.8</v>
+      </c>
+      <c r="C43" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="10" t="n">
         <v>2313.2</v>
       </c>
-      <c r="E38" s="10" t="n">
+      <c r="E43" s="10" t="n">
         <v>2796.3</v>
       </c>
-      <c r="F38" s="10" t="n">
+      <c r="F43" s="10" t="n">
         <v>6378.7</v>
       </c>
-      <c r="G38" s="10" t="n">
+      <c r="G43" s="10" t="n">
         <v>128.9</v>
       </c>
-      <c r="H38" s="10" t="n">
+      <c r="H43" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="10" t="n">
         <v>9303.9</v>
       </c>
-      <c r="I38" s="10" t="n">
+      <c r="J43" s="10" t="n">
         <v>9303.9</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="22" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
         <is>
           <t>Upside</t>
         </is>
       </c>
-      <c r="B39" s="10" t="n">
-        <v>4776.8</v>
-      </c>
-      <c r="C39" s="10" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D39" s="10" t="n">
+      <c r="B44" s="10" t="n">
+        <v>6276.8</v>
+      </c>
+      <c r="C44" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="10" t="n">
         <v>2250.3</v>
       </c>
-      <c r="E39" s="10" t="n">
+      <c r="E44" s="10" t="n">
         <v>5377.2</v>
       </c>
-      <c r="F39" s="10" t="n">
-        <v>2743.5</v>
-      </c>
-      <c r="G39" s="10" t="n">
+      <c r="F44" s="10" t="n">
+        <v>2043.5</v>
+      </c>
+      <c r="G44" s="10" t="n">
         <v>406.4</v>
       </c>
-      <c r="H39" s="10" t="n">
+      <c r="H44" s="10" t="n">
+        <v>700</v>
+      </c>
+      <c r="I44" s="10" t="n">
         <v>8527.1</v>
       </c>
-      <c r="I39" s="10" t="n">
+      <c r="J44" s="10" t="n">
         <v>8527.1</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="22" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="22" t="inlineStr">
         <is>
           <t>Downside</t>
         </is>
       </c>
-      <c r="B40" s="10" t="n">
-        <v>1169.2</v>
-      </c>
-      <c r="C40" s="10" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D40" s="10" t="n">
+      <c r="B45" s="10" t="n">
+        <v>2669.2</v>
+      </c>
+      <c r="C45" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D45" s="10" t="n">
         <v>2423.2</v>
       </c>
-      <c r="E40" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="10" t="n">
+      <c r="E45" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="10" t="n">
         <v>6387.5</v>
       </c>
-      <c r="G40" s="10" t="n">
+      <c r="G45" s="10" t="n">
         <v>-295.2</v>
       </c>
-      <c r="H40" s="10" t="n">
+      <c r="H45" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="10" t="n">
         <v>6092.3</v>
       </c>
-      <c r="I40" s="10" t="n">
+      <c r="J45" s="10" t="n">
         <v>6092.3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A39:H39"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A1:H1"/>
     <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/deliverables/Target_Cash_Flow_Investment_Capacity_Model.xlsx
+++ b/deliverables/Target_Cash_Flow_Investment_Capacity_Model.xlsx
@@ -3406,7 +3406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3998,7 +3998,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Corrected Capacity Taxonomy (Milestone 9 v2 correction): 18 named checks</t>
+          <t>Corrected Capacity Taxonomy (Milestone 9 v2 correction): 19 named checks</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
     <row r="54">
       <c r="A54" s="20" t="inlineStr">
         <is>
-          <t>opening_excess_liquidity_excluded_from_generation</t>
+          <t>net_horizon_capacity_reconciles</t>
         </is>
       </c>
       <c r="B54" s="22" t="n">
@@ -4279,14 +4279,14 @@
     <row r="55">
       <c r="A55" s="20" t="inlineStr">
         <is>
-          <t>operating_fcf_reconciles</t>
+          <t>opening_excess_liquidity_excluded_from_generation</t>
         </is>
       </c>
       <c r="B55" s="22" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C55" s="22" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D55" s="22" t="n">
         <v>0</v>
@@ -4298,7 +4298,7 @@
     <row r="56">
       <c r="A56" s="20" t="inlineStr">
         <is>
-          <t>post_dividend_generation_reconciles</t>
+          <t>operating_fcf_reconciles</t>
         </is>
       </c>
       <c r="B56" s="22" t="n">
@@ -4317,7 +4317,7 @@
     <row r="57">
       <c r="A57" s="20" t="inlineStr">
         <is>
-          <t>repurchases_in_discretionary_deployment</t>
+          <t>post_dividend_generation_reconciles</t>
         </is>
       </c>
       <c r="B57" s="22" t="n">
@@ -4336,7 +4336,7 @@
     <row r="58">
       <c r="A58" s="20" t="inlineStr">
         <is>
-          <t>scenario_and_cutoff_lineage_complete</t>
+          <t>repurchases_in_discretionary_deployment</t>
         </is>
       </c>
       <c r="B58" s="22" t="n">
@@ -4355,7 +4355,7 @@
     <row r="59">
       <c r="A59" s="20" t="inlineStr">
         <is>
-          <t>self_funded_generation_excludes_opening_liquidity</t>
+          <t>scenario_and_cutoff_lineage_complete</t>
         </is>
       </c>
       <c r="B59" s="22" t="n">
@@ -4371,10 +4371,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TOTAL: 210 results, 0 failures (7 further structural/definitional proofs live in tests/unit/test_capacity_taxonomy.py)</t>
+    <row r="60">
+      <c r="A60" s="20" t="inlineStr">
+        <is>
+          <t>self_funded_generation_excludes_opening_liquidity</t>
+        </is>
+      </c>
+      <c r="B60" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="C60" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="D60" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>TOTAL: 213 results, 0 failures (7 further structural/definitional proofs live in tests/unit/test_capacity_taxonomy.py)</t>
         </is>
       </c>
     </row>
@@ -8681,7 +8700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -9591,12 +9610,17 @@
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
-          <t>Total Horizon Capacity Accessible (C+A+B)</t>
+          <t>Gross Horizon Funding, Before Reserve Adjustments (C+A+B) -- NOT net accessible capacity</t>
         </is>
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>Reconciles To (D+E+Reserve Mvmt+Forward Reserve)</t>
+          <t>NET Horizon Deployable Capacity (Gross - Reserve Mvmt - Terminal Forward Reserve)</t>
+        </is>
+      </c>
+      <c r="K42" s="9" t="inlineStr">
+        <is>
+          <t>Reconciles To (D+E)</t>
         </is>
       </c>
     </row>
@@ -9630,8 +9654,11 @@
       <c r="I43" s="10" t="n">
         <v>9303.9</v>
       </c>
-      <c r="J43" s="10" t="n">
-        <v>9303.9</v>
+      <c r="J43" s="13" t="n">
+        <v>9175</v>
+      </c>
+      <c r="K43" s="10" t="n">
+        <v>9175</v>
       </c>
     </row>
     <row r="44">
@@ -9664,8 +9691,11 @@
       <c r="I44" s="10" t="n">
         <v>8527.1</v>
       </c>
-      <c r="J44" s="10" t="n">
-        <v>8527.1</v>
+      <c r="J44" s="13" t="n">
+        <v>7420.7</v>
+      </c>
+      <c r="K44" s="10" t="n">
+        <v>7420.7</v>
       </c>
     </row>
     <row r="45">
@@ -9698,8 +9728,11 @@
       <c r="I45" s="10" t="n">
         <v>6092.3</v>
       </c>
-      <c r="J45" s="10" t="n">
-        <v>6092.3</v>
+      <c r="J45" s="13" t="n">
+        <v>6387.5</v>
+      </c>
+      <c r="K45" s="10" t="n">
+        <v>6387.5</v>
       </c>
     </row>
   </sheetData>
